--- a/output/第10期計画_主張の根拠水準の棚卸しと再レビュー.xlsx
+++ b/output/第10期計画_主張の根拠水準の棚卸しと再レビュー.xlsx
@@ -670,7 +670,7 @@
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>全成果物の主要な主張46件を、領域別・根拠水準別に分類する。記述の形（断定・留保付き断定・推量・記述せず）を併記する。</t>
+          <t>全成果物の主要な主張54件を、領域別・根拠水準別に分類する。記述の形（断定・留保付き断定・推量・記述せず）を併記する。</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
@@ -919,12 +919,12 @@
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>C1、C2、C3、C4、C5</t>
+          <t>C1、C2、C3、C4、C5、C6、C7、C8、C9</t>
         </is>
       </c>
       <c r="D17" s="7" t="n"/>
       <c r="E17" s="8" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="18" ht="20" customHeight="1">
@@ -940,12 +940,12 @@
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>D1、D2、D3、D4、D5</t>
+          <t>D1、D2、D3、D4、D5、D6、D7</t>
         </is>
       </c>
       <c r="D18" s="7" t="n"/>
       <c r="E18" s="8" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="19" ht="20" customHeight="1">
@@ -1024,12 +1024,12 @@
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>H1、H2、H3、H4、H5、H6</t>
+          <t>H1、H2、H3、H4、H5、H6、H7、H8</t>
         </is>
       </c>
       <c r="D22" s="7" t="n"/>
       <c r="E22" s="8" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="23" ht="20" customHeight="1">
@@ -1122,7 +1122,7 @@
       </c>
       <c r="D28" s="7" t="n"/>
       <c r="E28" s="8" t="n">
-        <v>17</v>
+        <v>24</v>
       </c>
     </row>
     <row r="29" ht="32" customHeight="1">
@@ -1143,7 +1143,7 @@
       </c>
       <c r="D29" s="7" t="n"/>
       <c r="E29" s="8" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
     </row>
     <row r="30" ht="32" customHeight="1">
@@ -1164,7 +1164,7 @@
       </c>
       <c r="D30" s="7" t="n"/>
       <c r="E30" s="8" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="31" ht="32" customHeight="1">
@@ -1185,7 +1185,7 @@
       </c>
       <c r="D31" s="7" t="n"/>
       <c r="E31" s="8" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="33" ht="60" customHeight="1">
@@ -1227,7 +1227,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G52"/>
+  <dimension ref="A1:G60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -1242,7 +1242,7 @@
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>主張の棚卸し（46件）</t>
+          <t>主張の棚卸し（54件）</t>
         </is>
       </c>
     </row>
@@ -1636,7 +1636,7 @@
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>給付水準の高さは施設・居住系サービスの受給率と受給者単価に由来する</t>
+          <t>給付水準の高さは施設・居住系サービスの受給率と受給者単価がともに高いことによる</t>
         </is>
       </c>
       <c r="D14" s="13" t="inlineStr">
@@ -1651,17 +1651,17 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>見える化D49の地域差指数の分解（給付月額1.08＝認定率1.02・受給率1.08・受給者単価1.06）</t>
+          <t>見える化D49の4要素の水準（給付月額1.08・認定率1.02・受給率1.08・受給者単価1.06）。上川管内21保険者では給付月額指数の差を受給者単価が最もよく説明する（R²＝0.62）</t>
         </is>
       </c>
       <c r="G14" s="5" t="inlineStr">
         <is>
-          <t>3要素は独立ではない。施設が多ければ受給率も単価も同時に上がるため、「由来する」は要因の特定になっていない。区域外施設の利用の可能性も排除していない。自給率の算定により検証する（不足資料 No.6）</t>
+          <t>3要素は独立ではない（受給率と単価はr＝0.873）。さらに受給率×単価は給付月額指数に一致しない（大雪＋0.065、管内16/21で0.03超）。指数の分解による按分は撤回した（地域差の分析04・05シート）</t>
         </is>
       </c>
     </row>
     <row r="15" ht="52" customHeight="1">
-      <c r="A15" s="15" t="inlineStr">
+      <c r="A15" s="4" t="inlineStr">
         <is>
           <t>C2</t>
         </is>
@@ -1673,12 +1673,12 @@
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>全国との超過分はほぼ全て施設・居住系に由来する</t>
-        </is>
-      </c>
-      <c r="D15" s="13" t="inlineStr">
-        <is>
-          <t>E4</t>
+          <t>施設・居住系の受給率は在宅より全国比が高い（1.23対1.02）</t>
+        </is>
+      </c>
+      <c r="D15" s="11" t="inlineStr">
+        <is>
+          <t>E3</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -1688,12 +1688,12 @@
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>D41の受給率（在宅は全国比1.02、施設・居住系は同1.23）</t>
+          <t>見える化D41の受給率</t>
         </is>
       </c>
       <c r="G15" s="5" t="inlineStr">
         <is>
-          <t>C1と同じ。差の帰属を述べているが要因の特定ではない。「超過分は主に施設・居住系の受給率の差による」に改める</t>
+          <t>受給率の水準の対比としては確定している。超過分を要素別に按分する記述は撤回した（地域差の分析05シート）</t>
         </is>
       </c>
     </row>
@@ -1969,27 +1969,27 @@
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>施設・居住系の受給が区域外施設の利用による可能性がある</t>
-        </is>
-      </c>
-      <c r="D23" s="15" t="inlineStr">
-        <is>
-          <t>E5</t>
+          <t>施設・居住系の給付のうち区域外の事業所によるものは東川町23.2％・美瑛町24.7％・東神楽町34.5％である</t>
+        </is>
+      </c>
+      <c r="D23" s="9" t="inlineStr">
+        <is>
+          <t>E2</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
         <is>
-          <t>推量で記述</t>
+          <t>断定</t>
         </is>
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>定員が減少する一方で受給率が高いという不整合</t>
+          <t>見える化δ（介護サービス自給率・令和7年9月。令和8年7月30日受領）</t>
         </is>
       </c>
       <c r="G23" s="5" t="inlineStr">
         <is>
-          <t>自給率が未算定のため検証できない。推量の形で記述している</t>
+          <t>確定。定員が減少しても受給が維持されている背景が説明できた。ただし区域外利用が給付水準の高さの原因であるという部分は関係が確認できず（管内15件でr＝0.07）、記述しない</t>
         </is>
       </c>
     </row>
@@ -2660,7 +2660,7 @@
       </c>
     </row>
     <row r="42" ht="52" customHeight="1">
-      <c r="A42" s="15" t="inlineStr">
+      <c r="A42" s="4" t="inlineStr">
         <is>
           <t>H3</t>
         </is>
@@ -2675,9 +2675,9 @@
           <t>第9期は2年で約42百万円の剰余が生じている</t>
         </is>
       </c>
-      <c r="D42" s="13" t="inlineStr">
-        <is>
-          <t>E4</t>
+      <c r="D42" s="9" t="inlineStr">
+        <is>
+          <t>E2</t>
         </is>
       </c>
       <c r="E42" s="5" t="inlineStr">
@@ -2687,12 +2687,12 @@
       </c>
       <c r="F42" s="5" t="inlineStr">
         <is>
-          <t>必要保険料月額と条例基準額の差×被保険者数×12</t>
+          <t>見える化C1により令和6年度＋337円・令和7年度＋48円（累計385円／月）を確認。被保険者数約9,190人により金額換算</t>
         </is>
       </c>
       <c r="G42" s="5" t="inlineStr">
         <is>
-          <t>決算・基金の積立実績で確認していない（不足資料 No.9）</t>
+          <t>月額の差は原典で確定した。金額換算は被保険者数の前提を含む。基金への積立実績との一致は未確認（不足資料 No.9）。令和6・7年度は年度途中までの集計である</t>
         </is>
       </c>
     </row>
@@ -2712,24 +2712,24 @@
           <t>第7期の保険料基準額は6,077円である</t>
         </is>
       </c>
-      <c r="D43" s="15" t="inlineStr">
-        <is>
-          <t>E5</t>
+      <c r="D43" s="11" t="inlineStr">
+        <is>
+          <t>E3</t>
         </is>
       </c>
       <c r="E43" s="5" t="inlineStr">
         <is>
-          <t>訂正したが未確認</t>
+          <t>断定</t>
         </is>
       </c>
       <c r="F43" s="5" t="inlineStr">
         <is>
-          <t>剰余の累計＋159円との内部整合のみ</t>
+          <t>見える化C1（介護保険事業計画報告値・令和8年7月30日受領）により平成30年度〜令和2年度の第1号保険料月額として確認</t>
         </is>
       </c>
       <c r="G43" s="5" t="inlineStr">
         <is>
-          <t>条例で確認していない。＋159円自体の根拠も未確認（不足資料 No.10）</t>
+          <t>確定。内部整合による推定（剰余累計＋159円）が原典と一致した。不足資料No.10は解消</t>
         </is>
       </c>
     </row>
@@ -2810,22 +2810,22 @@
     <row r="46" ht="52" customHeight="1">
       <c r="A46" s="4" t="inlineStr">
         <is>
-          <t>I1</t>
+          <t>C6</t>
         </is>
       </c>
       <c r="B46" s="4" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C46" s="5" t="inlineStr">
         <is>
-          <t>特定地域の指定基準は3段階の構造である</t>
-        </is>
-      </c>
-      <c r="D46" s="9" t="inlineStr">
-        <is>
-          <t>E1</t>
+          <t>上川管内21保険者のなかでは、当広域連合の給付月額指数1.08は8〜10位（比布町・剣淵町と同値）であり管内中位値1.05に近い</t>
+        </is>
+      </c>
+      <c r="D46" s="11" t="inlineStr">
+        <is>
+          <t>E3</t>
         </is>
       </c>
       <c r="E46" s="5" t="inlineStr">
@@ -2835,34 +2835,34 @@
       </c>
       <c r="F46" s="5" t="inlineStr">
         <is>
-          <t>第135回社会保障審議会介護保険部会 資料3の直接確認</t>
+          <t>見える化D49（令和5年）。管内平均1.000、最大1.23（愛別町）、最小0.73（音威子府村）</t>
         </is>
       </c>
       <c r="G46" s="5" t="inlineStr">
         <is>
-          <t>告示前の素案である旨を明記済み</t>
+          <t>「全国を上回る」ことと「管内で高い」ことは別である</t>
         </is>
       </c>
     </row>
     <row r="47" ht="52" customHeight="1">
       <c r="A47" s="4" t="inlineStr">
         <is>
-          <t>I2</t>
+          <t>C7</t>
         </is>
       </c>
       <c r="B47" s="4" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C47" s="5" t="inlineStr">
         <is>
-          <t>3町の地域指定は東川＝辺地・特豪、美瑛＝過疎・辺地・特豪、東神楽＝辺地</t>
+          <t>地域差指数の受給率×受給者単価は給付月額指数に一致しない</t>
         </is>
       </c>
       <c r="D47" s="9" t="inlineStr">
         <is>
-          <t>E1</t>
+          <t>E2</t>
         </is>
       </c>
       <c r="E47" s="5" t="inlineStr">
@@ -2872,34 +2872,34 @@
       </c>
       <c r="F47" s="5" t="inlineStr">
         <is>
-          <t>地域指定一覧（令和8年4月1日現在）の直接確認</t>
+          <t>上川管内21保険者中16保険者で0.03を超えてずれる。全保険者で正の方向に偏る（平均＋0.063、大雪＋0.065）</t>
         </is>
       </c>
       <c r="G47" s="5" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>ずれが生じる理由（性・年齢調整の適用範囲、指数化の基準）は未確認（不足資料No.16）</t>
         </is>
       </c>
     </row>
     <row r="48" ht="52" customHeight="1">
       <c r="A48" s="4" t="inlineStr">
         <is>
-          <t>I3</t>
+          <t>C8</t>
         </is>
       </c>
       <c r="B48" s="4" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C48" s="5" t="inlineStr">
         <is>
-          <t>美瑛町の町道除雪率は52.9％、スクールバスは10路線である</t>
+          <t>給付水準の高さは平成21年度から続く構造であり、17年間の伸びは管内で小さい方に属する</t>
         </is>
       </c>
       <c r="D48" s="9" t="inlineStr">
         <is>
-          <t>E1</t>
+          <t>E2</t>
         </is>
       </c>
       <c r="E48" s="5" t="inlineStr">
@@ -2909,101 +2909,397 @@
       </c>
       <c r="F48" s="5" t="inlineStr">
         <is>
-          <t>美瑛町過疎地域持続的発展市町村計画の直接確認</t>
+          <t>見える化C1。平成21年度の給付月額21,490円は管内1位、令和7年度26,885円は12位。伸び率＋25.1％は管内16位（管内平均＋46.4％）</t>
         </is>
       </c>
       <c r="G48" s="5" t="inlineStr">
         <is>
-          <t>令和3〜7年度計画の値であり、最新の実績ではない</t>
+          <t>令和6・7年度は年度途中までの集計である</t>
         </is>
       </c>
     </row>
     <row r="49" ht="52" customHeight="1">
       <c r="A49" s="4" t="inlineStr">
         <is>
-          <t>I4</t>
+          <t>C9</t>
         </is>
       </c>
       <c r="B49" s="4" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C49" s="5" t="inlineStr">
         <is>
-          <t>朗根内地区は訪問・通所困難地域に該当する可能性が最も高い</t>
-        </is>
-      </c>
-      <c r="D49" s="13" t="inlineStr">
-        <is>
-          <t>E4</t>
+          <t>令和7年度の必要保険料月額は6,352円で基準額6,400円との差は48円である</t>
+        </is>
+      </c>
+      <c r="D49" s="11" t="inlineStr">
+        <is>
+          <t>E3</t>
         </is>
       </c>
       <c r="E49" s="5" t="inlineStr">
         <is>
-          <t>推量で記述</t>
+          <t>断定</t>
         </is>
       </c>
       <c r="F49" s="5" t="inlineStr">
         <is>
-          <t>人口233人、スクールバス依存、除雪率52.9％の組合せ</t>
+          <t>見える化C1。令和6年度の337円から縮小</t>
         </is>
       </c>
       <c r="G49" s="5" t="inlineStr">
         <is>
-          <t>事業所の通常の事業の実施地域を確認していないため、判定の根拠そのものが未取得（不足資料 No.2）</t>
+          <t>年度途中までの集計であり確定値により再計算する</t>
         </is>
       </c>
     </row>
     <row r="50" ht="52" customHeight="1">
       <c r="A50" s="4" t="inlineStr">
         <is>
+          <t>D6</t>
+        </is>
+      </c>
+      <c r="B50" s="4" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="C50" s="5" t="inlineStr">
+        <is>
+          <t>3町の6区分平均の自給率は美瑛77.5％・東川67.1％・東神楽63.2％である</t>
+        </is>
+      </c>
+      <c r="D50" s="9" t="inlineStr">
+        <is>
+          <t>E2</t>
+        </is>
+      </c>
+      <c r="E50" s="5" t="inlineStr">
+        <is>
+          <t>断定</t>
+        </is>
+      </c>
+      <c r="F50" s="5" t="inlineStr">
+        <is>
+          <t>見える化δ（令和7年9月）から算定</t>
+        </is>
+      </c>
+      <c r="G50" s="5" t="inlineStr">
+        <is>
+          <t>算定できる区分の単純平均である。給付額による加重平均には町別のサービス区分別給付費を要する（不足資料No.17）</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="52" customHeight="1">
+      <c r="A51" s="4" t="inlineStr">
+        <is>
+          <t>D7</t>
+        </is>
+      </c>
+      <c r="B51" s="4" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="C51" s="5" t="inlineStr">
+        <is>
+          <t>自給率と給付月額指数の間に関係は確認できない</t>
+        </is>
+      </c>
+      <c r="D51" s="9" t="inlineStr">
+        <is>
+          <t>E2</t>
+        </is>
+      </c>
+      <c r="E51" s="5" t="inlineStr">
+        <is>
+          <t>断定</t>
+        </is>
+      </c>
+      <c r="F51" s="5" t="inlineStr">
+        <is>
+          <t>単一市町村保険者のうち自給率0.0％の2村を除く15件でr＝0.07</t>
+        </is>
+      </c>
+      <c r="G51" s="5" t="inlineStr">
+        <is>
+          <t>2村を含めるとr＝0.53となるため、除外の理由を必ず併記する</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="52" customHeight="1">
+      <c r="A52" s="4" t="inlineStr">
+        <is>
+          <t>H7</t>
+        </is>
+      </c>
+      <c r="B52" s="4" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="C52" s="5" t="inlineStr">
+        <is>
+          <t>保険料基準額の推移は第5期5,100円→第6期5,776円→第7期6,077円→第8期6,300円→第9期6,400円である</t>
+        </is>
+      </c>
+      <c r="D52" s="11" t="inlineStr">
+        <is>
+          <t>E3</t>
+        </is>
+      </c>
+      <c r="E52" s="5" t="inlineStr">
+        <is>
+          <t>断定</t>
+        </is>
+      </c>
+      <c r="F52" s="5" t="inlineStr">
+        <is>
+          <t>見える化C1（介護保険事業計画報告値）</t>
+        </is>
+      </c>
+      <c r="G52" s="5" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="52" customHeight="1">
+      <c r="A53" s="4" t="inlineStr">
+        <is>
+          <t>H8</t>
+        </is>
+      </c>
+      <c r="B53" s="4" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="C53" s="5" t="inlineStr">
+        <is>
+          <t>第9期において保険料が必要額を上回っている保険者は上川管内21のうち6にとどまる</t>
+        </is>
+      </c>
+      <c r="D53" s="9" t="inlineStr">
+        <is>
+          <t>E2</t>
+        </is>
+      </c>
+      <c r="E53" s="5" t="inlineStr">
+        <is>
+          <t>断定</t>
+        </is>
+      </c>
+      <c r="F53" s="5" t="inlineStr">
+        <is>
+          <t>見える化C1から算定。管内平均は▲400円で当広域連合の＋385円は逆方向</t>
+        </is>
+      </c>
+      <c r="G53" s="5" t="inlineStr">
+        <is>
+          <t>令和6・7年度は年度途中までの集計である</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="52" customHeight="1">
+      <c r="A54" s="4" t="inlineStr">
+        <is>
+          <t>I1</t>
+        </is>
+      </c>
+      <c r="B54" s="4" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="C54" s="5" t="inlineStr">
+        <is>
+          <t>特定地域の指定基準は3段階の構造である</t>
+        </is>
+      </c>
+      <c r="D54" s="9" t="inlineStr">
+        <is>
+          <t>E1</t>
+        </is>
+      </c>
+      <c r="E54" s="5" t="inlineStr">
+        <is>
+          <t>断定</t>
+        </is>
+      </c>
+      <c r="F54" s="5" t="inlineStr">
+        <is>
+          <t>第135回社会保障審議会介護保険部会 資料3の直接確認</t>
+        </is>
+      </c>
+      <c r="G54" s="5" t="inlineStr">
+        <is>
+          <t>告示前の素案である旨を明記済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="52" customHeight="1">
+      <c r="A55" s="4" t="inlineStr">
+        <is>
+          <t>I2</t>
+        </is>
+      </c>
+      <c r="B55" s="4" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="C55" s="5" t="inlineStr">
+        <is>
+          <t>3町の地域指定は東川＝辺地・特豪、美瑛＝過疎・辺地・特豪、東神楽＝辺地</t>
+        </is>
+      </c>
+      <c r="D55" s="9" t="inlineStr">
+        <is>
+          <t>E1</t>
+        </is>
+      </c>
+      <c r="E55" s="5" t="inlineStr">
+        <is>
+          <t>断定</t>
+        </is>
+      </c>
+      <c r="F55" s="5" t="inlineStr">
+        <is>
+          <t>地域指定一覧（令和8年4月1日現在）の直接確認</t>
+        </is>
+      </c>
+      <c r="G55" s="5" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="52" customHeight="1">
+      <c r="A56" s="4" t="inlineStr">
+        <is>
+          <t>I3</t>
+        </is>
+      </c>
+      <c r="B56" s="4" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="C56" s="5" t="inlineStr">
+        <is>
+          <t>美瑛町の町道除雪率は52.9％、スクールバスは10路線である</t>
+        </is>
+      </c>
+      <c r="D56" s="9" t="inlineStr">
+        <is>
+          <t>E1</t>
+        </is>
+      </c>
+      <c r="E56" s="5" t="inlineStr">
+        <is>
+          <t>断定</t>
+        </is>
+      </c>
+      <c r="F56" s="5" t="inlineStr">
+        <is>
+          <t>美瑛町過疎地域持続的発展市町村計画の直接確認</t>
+        </is>
+      </c>
+      <c r="G56" s="5" t="inlineStr">
+        <is>
+          <t>令和3〜7年度計画の値であり、最新の実績ではない</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="52" customHeight="1">
+      <c r="A57" s="4" t="inlineStr">
+        <is>
+          <t>I4</t>
+        </is>
+      </c>
+      <c r="B57" s="4" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="C57" s="5" t="inlineStr">
+        <is>
+          <t>朗根内地区は訪問・通所困難地域に該当する可能性が最も高い</t>
+        </is>
+      </c>
+      <c r="D57" s="13" t="inlineStr">
+        <is>
+          <t>E4</t>
+        </is>
+      </c>
+      <c r="E57" s="5" t="inlineStr">
+        <is>
+          <t>推量で記述</t>
+        </is>
+      </c>
+      <c r="F57" s="5" t="inlineStr">
+        <is>
+          <t>人口233人、スクールバス依存、除雪率52.9％の組合せ</t>
+        </is>
+      </c>
+      <c r="G57" s="5" t="inlineStr">
+        <is>
+          <t>事業所の通常の事業の実施地域を確認していないため、判定の根拠そのものが未取得（不足資料 No.2）</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="52" customHeight="1">
+      <c r="A58" s="4" t="inlineStr">
+        <is>
           <t>I5</t>
         </is>
       </c>
-      <c r="B50" s="4" t="inlineStr">
+      <c r="B58" s="4" t="inlineStr">
         <is>
           <t>I</t>
         </is>
       </c>
-      <c r="C50" s="5" t="inlineStr">
+      <c r="C58" s="5" t="inlineStr">
         <is>
           <t>小学校区と第9期の6圏域の対応関係</t>
         </is>
       </c>
-      <c r="D50" s="15" t="inlineStr">
+      <c r="D58" s="15" t="inlineStr">
         <is>
           <t>E5</t>
         </is>
       </c>
-      <c r="E50" s="5" t="inlineStr">
+      <c r="E58" s="5" t="inlineStr">
         <is>
           <t>記述せず</t>
         </is>
       </c>
-      <c r="F50" s="5" t="inlineStr">
+      <c r="F58" s="5" t="inlineStr">
         <is>
           <t>―</t>
         </is>
       </c>
-      <c r="G50" s="5" t="inlineStr">
+      <c r="G58" s="5" t="inlineStr">
         <is>
           <t>美馬牛小学校区以外は対応が不明。美瑛町への確認を要する（不足資料 No.12）</t>
         </is>
       </c>
     </row>
-    <row r="52" ht="48" customHeight="1">
-      <c r="A52" s="17" t="inlineStr">
-        <is>
-          <t>注1）No.の網掛けは、E4・E5でありながら断定形で記述しているもの（8件）である。03シートで対応を示す。注2）「記述の形」の区分は次のとおり。断定＝「〜である」「〜します」等の断定形。断定（留保付き）＝断定形だが留保を併記している。推量で記述＝「〜の可能性がある」「〜と考えられる」等。記述せず＝主張として書いていない。前提の選択として明示＝推計の前提であり事実の主張ではないことを明示。注3）本表の46件は、成果物に含まれる主要な主張を網羅する意図で領域ごとに抽出したものである。数値の引用や図表の説明など、事実の記述にとどまるものは含めていない。</t>
+    <row r="60" ht="48" customHeight="1">
+      <c r="A60" s="17" t="inlineStr">
+        <is>
+          <t>注1）No.の網掛けは、E4・E5でありながら断定形で記述しているもの（8件）である。03シートで対応を示す。注2）「記述の形」の区分は次のとおり。断定＝「〜である」「〜します」等の断定形。断定（留保付き）＝断定形だが留保を併記している。推量で記述＝「〜の可能性がある」「〜と考えられる」等。記述せず＝主張として書いていない。前提の選択として明示＝推計の前提であり事実の主張ではないことを明示。注3）本表の54件は、成果物に含まれる主要な主張を網羅する意図で領域ごとに抽出したものである。数値の引用や図表の説明など、事実の記述にとどまるものは含めていない。</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="3">
+    <mergeCell ref="A60:G60"/>
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A52:G52"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3187,23 +3483,23 @@
         <v>0</v>
       </c>
       <c r="D7" s="8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E7" s="8" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F7" s="8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G7" s="8" t="n">
         <v>0</v>
       </c>
       <c r="H7" s="8" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="I7" s="15" t="inlineStr">
         <is>
-          <t>60％</t>
+          <t>22％</t>
         </is>
       </c>
       <c r="J7" s="5" t="inlineStr">
@@ -3227,7 +3523,7 @@
         <v>0</v>
       </c>
       <c r="D8" s="8" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E8" s="8" t="n">
         <v>1</v>
@@ -3236,14 +3532,14 @@
         <v>0</v>
       </c>
       <c r="G8" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H8" s="8" t="n">
-        <v>5</v>
-      </c>
-      <c r="I8" s="15" t="inlineStr">
-        <is>
-          <t>40％</t>
+        <v>7</v>
+      </c>
+      <c r="I8" s="13" t="inlineStr">
+        <is>
+          <t>14％</t>
         </is>
       </c>
       <c r="J8" s="5" t="inlineStr">
@@ -3383,23 +3679,23 @@
         <v>0</v>
       </c>
       <c r="D12" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="E12" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="E12" s="8" t="n">
-        <v>1</v>
-      </c>
       <c r="F12" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G12" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H12" s="8" t="n">
-        <v>6</v>
-      </c>
-      <c r="I12" s="15" t="inlineStr">
-        <is>
-          <t>33％</t>
+        <v>8</v>
+      </c>
+      <c r="I12" s="9" t="inlineStr">
+        <is>
+          <t>0％</t>
         </is>
       </c>
       <c r="J12" s="5" t="inlineStr"/>
@@ -3455,23 +3751,23 @@
         <v>4</v>
       </c>
       <c r="D14" s="20" t="n">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="E14" s="20" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="F14" s="20" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G14" s="20" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="H14" s="20" t="n">
-        <v>46</v>
+        <v>54</v>
       </c>
       <c r="I14" s="19" t="inlineStr">
         <is>
-          <t>37％</t>
+          <t>24％</t>
         </is>
       </c>
       <c r="J14" s="19" t="inlineStr"/>
@@ -3566,7 +3862,7 @@
         </is>
       </c>
       <c r="B19" s="8" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="C19" s="8" t="n">
         <v>1</v>
@@ -3581,7 +3877,7 @@
         <v>0</v>
       </c>
       <c r="G19" s="8" t="n">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="H19" s="5" t="inlineStr"/>
       <c r="I19" s="5" t="inlineStr"/>
@@ -3598,7 +3894,7 @@
         </is>
       </c>
       <c r="B20" s="8" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="C20" s="8" t="n">
         <v>0</v>
@@ -3613,7 +3909,7 @@
         <v>0</v>
       </c>
       <c r="G20" s="8" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="H20" s="5" t="inlineStr"/>
       <c r="I20" s="5" t="inlineStr"/>
@@ -3626,7 +3922,7 @@
         </is>
       </c>
       <c r="B21" s="21" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C21" s="8" t="n">
         <v>0</v>
@@ -3641,7 +3937,7 @@
         <v>0</v>
       </c>
       <c r="G21" s="8" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="H21" s="5" t="inlineStr"/>
       <c r="I21" s="5" t="inlineStr"/>
@@ -3664,7 +3960,7 @@
         <v>0</v>
       </c>
       <c r="D22" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E22" s="8" t="n">
         <v>3</v>
@@ -3673,7 +3969,7 @@
         <v>1</v>
       </c>
       <c r="G22" s="8" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="H22" s="5" t="inlineStr"/>
       <c r="I22" s="5" t="inlineStr"/>
@@ -3686,7 +3982,7 @@
     <row r="24" ht="28" customHeight="1">
       <c r="A24" s="17" t="inlineStr">
         <is>
-          <t>注1）E4・E5は合わせて17件で全体の37％を占める。このうち断定形で記述しているのは8件であり、03シートで対応する。注2）領域別では、C（給付費・受給率・単価）とD（供給基盤）でE4・E5の割合が高い。いずれも保険者・3町が保有する台帳・実績データを要するものであり、資料の受領により水準を引き上げられる。注3）F（住民の状態・行動）は個票データを受領しているためE2が多い。調査に基づく主張は根拠の水準が高い。</t>
+          <t>注1）E4・E5は合わせて13件で全体の24％を占める。このうち断定形で記述しているのは6件であり、03シートで対応する。注2）領域別では、C（給付費・受給率・単価）とD（供給基盤）でE4・E5の割合が高い。いずれも保険者・3町が保有する台帳・実績データを要するものであり、資料の受領により水準を引き上げられる。注3）F（住民の状態・行動）は個票データを受領しているためE2が多い。調査に基づく主張は根拠の水準が高い。</t>
         </is>
       </c>
     </row>
@@ -3707,7 +4003,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G14"/>
+  <dimension ref="A1:G12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -3722,7 +4018,7 @@
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>推論・仮説を断定形で記述している箇所（8件）</t>
+          <t>推論・仮説を断定形で記述している箇所（6件）</t>
         </is>
       </c>
     </row>
@@ -3820,7 +4116,7 @@
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>給付水準の高さは施設・居住系サービスの受給率と受給者単価に由来する</t>
+          <t>給付水準の高さは施設・居住系サービスの受給率と受給者単価がともに高いことによる</t>
         </is>
       </c>
       <c r="D6" s="13" t="inlineStr">
@@ -3847,7 +4143,7 @@
     <row r="7" ht="76" customHeight="1">
       <c r="A7" s="15" t="inlineStr">
         <is>
-          <t>C2</t>
+          <t>C3</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
@@ -3857,7 +4153,7 @@
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>全国との超過分はほぼ全て施設・居住系に由来する</t>
+          <t>受給率の低下分のほぼ全てが要介護5に由来する</t>
         </is>
       </c>
       <c r="D7" s="13" t="inlineStr">
@@ -3867,108 +4163,108 @@
       </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
-          <t>全国との差の大半は、施設・居住系サービスの受給率の差による</t>
+          <t>受給率の低下分の大半は、要介護5の受給率の低下による</t>
         </is>
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>差の帰属を述べているが、なぜその差が生じたかを特定していない</t>
+          <t>要介護5の受給者が減った理由（死亡・施設入所・認定の変化）を特定していない</t>
         </is>
       </c>
       <c r="G7" s="5" t="inlineStr">
         <is>
-          <t>不足資料 No.6</t>
+          <t>不足資料 No.8</t>
         </is>
       </c>
     </row>
     <row r="8" ht="76" customHeight="1">
       <c r="A8" s="15" t="inlineStr">
         <is>
-          <t>C3</t>
+          <t>D3</t>
         </is>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>受給率の低下分のほぼ全てが要介護5に由来する</t>
-        </is>
-      </c>
-      <c r="D8" s="13" t="inlineStr">
-        <is>
-          <t>E4</t>
+          <t>地域密着型通所介護の給付減は稼働率の低下によるものである</t>
+        </is>
+      </c>
+      <c r="D8" s="15" t="inlineStr">
+        <is>
+          <t>E5</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
-          <t>受給率の低下分の大半は、要介護5の受給率の低下による</t>
+          <t>地域密着型通所介護は、事業所数が4で不変かつ従事者が増加する一方で給付費が27.0％減少しており、稼働率の低下が疑われる</t>
         </is>
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>要介護5の受給者が減った理由（死亡・施設入所・認定の変化）を特定していない</t>
+          <t>稼働率そのものを確認していない。利用者1人あたりの利用回数の減少や、要介護度の変化による可能性もある</t>
         </is>
       </c>
       <c r="G8" s="5" t="inlineStr">
         <is>
-          <t>不足資料 No.8</t>
+          <t>不足資料 No.7</t>
         </is>
       </c>
     </row>
     <row r="9" ht="76" customHeight="1">
       <c r="A9" s="15" t="inlineStr">
         <is>
-          <t>D3</t>
+          <t>F4</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>F</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>地域密着型通所介護の給付減は稼働率の低下によるものである</t>
-        </is>
-      </c>
-      <c r="D9" s="15" t="inlineStr">
-        <is>
-          <t>E5</t>
+          <t>施設入所志向は心身の状態や経済状況ではなく支え手の有無で決まる</t>
+        </is>
+      </c>
+      <c r="D9" s="13" t="inlineStr">
+        <is>
+          <t>E4</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
         <is>
-          <t>地域密着型通所介護は、事業所数が4で不変かつ従事者が増加する一方で給付費が27.0％減少しており、稼働率の低下が疑われる</t>
+          <t>施設入所志向は、心身の状態や経済状況よりも、独居であることや世話をしてくれる人がいないことと強く結びついている</t>
         </is>
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>稼働率そのものを確認していない。利用者1人あたりの利用回数の減少や、要介護度の変化による可能性もある</t>
+          <t>「有意差がない」ことは「関係がない」ことを意味しない。標本規模による検出力を検討していない</t>
         </is>
       </c>
       <c r="G9" s="5" t="inlineStr">
         <is>
-          <t>不足資料 No.7</t>
+          <t>追加の資料は不要（記述の限定で対応）</t>
         </is>
       </c>
     </row>
     <row r="10" ht="76" customHeight="1">
       <c r="A10" s="15" t="inlineStr">
         <is>
-          <t>F4</t>
+          <t>G3</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>G</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>施設入所志向は心身の状態や経済状況ではなく支え手の有無で決まる</t>
+          <t>令和5年調査の交付金得点は第8期の取組を反映している</t>
         </is>
       </c>
       <c r="D10" s="13" t="inlineStr">
@@ -3978,96 +4274,22 @@
       </c>
       <c r="E10" s="5" t="inlineStr">
         <is>
-          <t>施設入所志向は、心身の状態や経済状況よりも、独居であることや世話をしてくれる人がいないことと強く結びついている</t>
+          <t>交付金の得点は令和5年度に実施された調査によるものであり、第9期（令和6年度〜）の取組は反映されていない</t>
         </is>
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>「有意差がない」ことは「関係がない」ことを意味しない。標本規模による検出力を検討していない</t>
+          <t>調査要領で評価対象期間を直接確認していない</t>
         </is>
       </c>
       <c r="G10" s="5" t="inlineStr">
         <is>
-          <t>追加の資料は不要（記述の限定で対応）</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="76" customHeight="1">
-      <c r="A11" s="15" t="inlineStr">
-        <is>
-          <t>G3</t>
-        </is>
-      </c>
-      <c r="B11" s="4" t="inlineStr">
-        <is>
-          <t>G</t>
-        </is>
-      </c>
-      <c r="C11" s="5" t="inlineStr">
-        <is>
-          <t>令和5年調査の交付金得点は第8期の取組を反映している</t>
-        </is>
-      </c>
-      <c r="D11" s="13" t="inlineStr">
-        <is>
-          <t>E4</t>
-        </is>
-      </c>
-      <c r="E11" s="5" t="inlineStr">
-        <is>
-          <t>交付金の得点は令和5年度に実施された調査によるものであり、第9期（令和6年度〜）の取組は反映されていない</t>
-        </is>
-      </c>
-      <c r="F11" s="5" t="inlineStr">
-        <is>
-          <t>調査要領で評価対象期間を直接確認していない</t>
-        </is>
-      </c>
-      <c r="G11" s="5" t="inlineStr">
-        <is>
           <t>不足資料 No.5</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="76" customHeight="1">
-      <c r="A12" s="15" t="inlineStr">
-        <is>
-          <t>H3</t>
-        </is>
-      </c>
-      <c r="B12" s="4" t="inlineStr">
-        <is>
-          <t>H</t>
-        </is>
-      </c>
-      <c r="C12" s="5" t="inlineStr">
-        <is>
-          <t>第9期は2年で約42百万円の剰余が生じている</t>
-        </is>
-      </c>
-      <c r="D12" s="13" t="inlineStr">
-        <is>
-          <t>E4</t>
-        </is>
-      </c>
-      <c r="E12" s="5" t="inlineStr">
-        <is>
-          <t>―</t>
-        </is>
-      </c>
-      <c r="F12" s="5" t="inlineStr">
-        <is>
-          <t>―</t>
-        </is>
-      </c>
-      <c r="G12" s="5" t="inlineStr">
-        <is>
-          <t>―</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="36" customHeight="1">
-      <c r="A14" s="17" t="inlineStr">
+    <row r="12" ht="36" customHeight="1">
+      <c r="A12" s="17" t="inlineStr">
         <is>
           <t>注1）8件のうち6件（A1・C1・C2・C3・D3・D4・F4・G3のうちF4を除く7件から資料不要のものを除く）は、資料の受領により水準を引き上げられる。F4は記述の限定のみで対応できる。注2）これらは、レッドチームレビューで逆転した2件と同じ構造を持つ。①部分的な観測から全体を述べている（A1・C2・C3）、②観測を説明する仮説を検証せずに事実として記述している（C1・D3・F4・G3）。注3）改める記述は、事実として確認できる部分と、推論にとどまる部分を分けて書いたものである。計画本文でも同じ方針で記述する。</t>
         </is>
@@ -4075,9 +4297,9 @@
     </row>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="A14:G14"/>
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A12:G12"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4755,7 +4977,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H28"/>
+  <dimension ref="A1:H31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -4771,7 +4993,7 @@
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>不足資料一覧（15件）</t>
+          <t>不足資料一覧（18件）</t>
         </is>
       </c>
     </row>
@@ -5226,111 +5448,111 @@
     </row>
     <row r="15" ht="64" customHeight="1">
       <c r="A15" s="4" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>第7期（平成30〜令和2年度）の保険料条例</t>
+          <t>町別・サービス区分別の給付費（令和4〜7年度）</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>基準額が6,077円か5,900円かを確定する。</t>
+          <t>自給率と掛け合わせて区域外への給付費の流出額を算定する。自給率の加重平均の算定にも必要。</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
         <is>
-          <t>H4の確定</t>
+          <t>D6の精緻化、給付費の地域内還流の議論</t>
         </is>
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>発注者</t>
+          <t>発注者・国保連</t>
         </is>
       </c>
       <c r="G15" s="4" t="inlineStr">
         <is>
-          <t>R8.9</t>
-        </is>
-      </c>
-      <c r="H15" s="11" t="inlineStr">
-        <is>
-          <t>中</t>
+          <t>R8.10</t>
+        </is>
+      </c>
+      <c r="H15" s="13" t="inlineStr">
+        <is>
+          <t>高</t>
         </is>
       </c>
     </row>
     <row r="16" ht="64" customHeight="1">
       <c r="A16" s="4" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>D</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>小学校区と日常生活圏域の対応関係</t>
+          <t>指定事業所台帳（区域外事業所の所在地）</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>健康とくらしの調査の分析地域1（小学校区12地区）と第9期の6圏域の対応。美馬牛小学校区以外が不明。</t>
+          <t>区域外の事業所が旭川市か他の市町村かを特定する。圏域を越えた利用の調整（第6章第4節）の根拠となる。</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
         <is>
-          <t>I5の確定、圏域別分析</t>
+          <t>区域外利用の内訳</t>
         </is>
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>美瑛町・3町</t>
+          <t>発注者・国保連</t>
         </is>
       </c>
       <c r="G16" s="4" t="inlineStr">
         <is>
-          <t>R8.9</t>
-        </is>
-      </c>
-      <c r="H16" s="11" t="inlineStr">
-        <is>
-          <t>中</t>
+          <t>R8.10</t>
+        </is>
+      </c>
+      <c r="H16" s="13" t="inlineStr">
+        <is>
+          <t>高</t>
         </is>
       </c>
     </row>
     <row r="17" ht="64" customHeight="1">
       <c r="A17" s="4" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>I</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>第9期の自己評価と北海道への報告の実績</t>
+          <t>小学校区と日常生活圏域の対応関係</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>介護保険法第117条に基づく評価・公表の実績。受託者の評価との対照に必要。</t>
+          <t>健康とくらしの調査の分析地域1（小学校区12地区）と第9期の6圏域の対応。美馬牛小学校区以外が不明。</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
-          <t>評価の枠組みの整理</t>
+          <t>I5の確定、圏域別分析</t>
         </is>
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>発注者</t>
+          <t>美瑛町・3町</t>
         </is>
       </c>
       <c r="G17" s="4" t="inlineStr">
@@ -5346,31 +5568,31 @@
     </row>
     <row r="18" ht="64" customHeight="1">
       <c r="A18" s="4" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>G</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>見える化B5a・B6a・B6bの令和8年3月末の値</t>
+          <t>第9期の自己評価と北海道への報告の実績</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>調整済み認定率は令和7年3月末までしか出力されていない。第9期の評価には令和8年3月末（令和7年度末）の値が必要。</t>
+          <t>介護保険法第117条に基づく評価・公表の実績。受託者の評価との対照に必要。</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
         <is>
-          <t>B3の主張の更新</t>
+          <t>評価の枠組みの整理</t>
         </is>
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>見える化システム</t>
+          <t>発注者</t>
         </is>
       </c>
       <c r="G18" s="4" t="inlineStr">
@@ -5378,145 +5600,205 @@
           <t>R8.9</t>
         </is>
       </c>
-      <c r="H18" s="22" t="inlineStr">
-        <is>
-          <t>低</t>
+      <c r="H18" s="11" t="inlineStr">
+        <is>
+          <t>中</t>
         </is>
       </c>
     </row>
     <row r="19" ht="64" customHeight="1">
       <c r="A19" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>見える化システムD49の指標定義</t>
+        </is>
+      </c>
+      <c r="D19" s="5" t="inlineStr">
+        <is>
+          <t>性・年齢調整の適用範囲と指数化の基準。受給率×受給者単価が給付月額指数に一致しない理由の特定に必要。</t>
+        </is>
+      </c>
+      <c r="E19" s="5" t="inlineStr">
+        <is>
+          <t>C7の説明</t>
+        </is>
+      </c>
+      <c r="F19" s="5" t="inlineStr">
+        <is>
+          <t>見える化システム・厚生労働省</t>
+        </is>
+      </c>
+      <c r="G19" s="4" t="inlineStr">
+        <is>
+          <t>R8.10</t>
+        </is>
+      </c>
+      <c r="H19" s="11" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="64" customHeight="1">
+      <c r="A20" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="B20" s="4" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>見える化B5a・B6a・B6bの令和8年3月末の値</t>
+        </is>
+      </c>
+      <c r="D20" s="5" t="inlineStr">
+        <is>
+          <t>調整済み認定率は令和7年3月末までしか出力されていない。第9期の評価には令和8年3月末（令和7年度末）の値が必要。</t>
+        </is>
+      </c>
+      <c r="E20" s="5" t="inlineStr">
+        <is>
+          <t>B3の主張の更新</t>
+        </is>
+      </c>
+      <c r="F20" s="5" t="inlineStr">
+        <is>
+          <t>見える化システム</t>
+        </is>
+      </c>
+      <c r="G20" s="4" t="inlineStr">
+        <is>
+          <t>R8.9</t>
+        </is>
+      </c>
+      <c r="H20" s="22" t="inlineStr">
+        <is>
+          <t>低</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="64" customHeight="1">
+      <c r="A21" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="B19" s="4" t="inlineStr">
+      <c r="B21" s="4" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="C19" s="5" t="inlineStr">
+      <c r="C21" s="5" t="inlineStr">
         <is>
           <t>令和7年国勢調査による町別の高齢者を含む世帯</t>
         </is>
       </c>
-      <c r="D19" s="5" t="inlineStr">
+      <c r="D21" s="5" t="inlineStr">
         <is>
           <t>高齢者単身世帯・夫婦世帯の最新値。公表され次第。</t>
         </is>
       </c>
-      <c r="E19" s="5" t="inlineStr">
+      <c r="E21" s="5" t="inlineStr">
         <is>
           <t>A4の更新</t>
         </is>
       </c>
-      <c r="F19" s="5" t="inlineStr">
+      <c r="F21" s="5" t="inlineStr">
         <is>
           <t>総務省・3町</t>
         </is>
       </c>
-      <c r="G19" s="4" t="inlineStr">
+      <c r="G21" s="4" t="inlineStr">
         <is>
           <t>公表後</t>
         </is>
       </c>
-      <c r="H19" s="22" t="inlineStr">
+      <c r="H21" s="22" t="inlineStr">
         <is>
           <t>低</t>
         </is>
       </c>
     </row>
-    <row r="21" ht="20" customHeight="1">
-      <c r="A21" s="6" t="inlineStr">
+    <row r="22" ht="64" customHeight="1">
+      <c r="A22" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="B22" s="4" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>第7期（平成30〜令和2年度）の保険料条例（解消済）</t>
+        </is>
+      </c>
+      <c r="D22" s="5" t="inlineStr">
+        <is>
+          <t>見える化C1（令和8年7月30日受領）により6,077円を確認した。条例による確認は不要となった。</t>
+        </is>
+      </c>
+      <c r="E22" s="5" t="inlineStr">
+        <is>
+          <t>H4の確定（解消）</t>
+        </is>
+      </c>
+      <c r="F22" s="5" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="G22" s="4" t="inlineStr">
+        <is>
+          <t>解消</t>
+        </is>
+      </c>
+      <c r="H22" s="22" t="inlineStr">
+        <is>
+          <t>低</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="20" customHeight="1">
+      <c r="A24" s="6" t="inlineStr">
         <is>
           <t>【優先度別の集計】</t>
         </is>
       </c>
     </row>
-    <row r="22" ht="30" customHeight="1">
-      <c r="A22" s="3" t="inlineStr">
+    <row r="25" ht="30" customHeight="1">
+      <c r="A25" s="3" t="inlineStr">
         <is>
           <t>優先度</t>
         </is>
       </c>
-      <c r="B22" s="3" t="inlineStr">
+      <c r="B25" s="3" t="inlineStr">
         <is>
           <t>件数</t>
         </is>
       </c>
-      <c r="C22" s="3" t="inlineStr">
+      <c r="C25" s="3" t="inlineStr">
         <is>
           <t>内容</t>
         </is>
       </c>
-      <c r="D22" s="3" t="inlineStr"/>
-      <c r="E22" s="3" t="inlineStr"/>
-      <c r="F22" s="3" t="inlineStr"/>
-      <c r="G22" s="3" t="inlineStr"/>
-      <c r="H22" s="3" t="inlineStr"/>
-    </row>
-    <row r="23" ht="32" customHeight="1">
-      <c r="A23" s="16" t="inlineStr">
+      <c r="D25" s="3" t="inlineStr"/>
+      <c r="E25" s="3" t="inlineStr"/>
+      <c r="F25" s="3" t="inlineStr"/>
+      <c r="G25" s="3" t="inlineStr"/>
+      <c r="H25" s="3" t="inlineStr"/>
+    </row>
+    <row r="26" ht="32" customHeight="1">
+      <c r="A26" s="16" t="inlineStr">
         <is>
           <t>最高</t>
-        </is>
-      </c>
-      <c r="B23" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="C23" s="5" t="inlineStr">
-        <is>
-          <t>No.13 令和6〜8年度の施策・事業実績、事業量、、No.14 在宅生活改善調査・居所変更実態調査・介護</t>
-        </is>
-      </c>
-      <c r="D23" s="23" t="n"/>
-      <c r="E23" s="23" t="n"/>
-      <c r="F23" s="23" t="n"/>
-      <c r="G23" s="23" t="n"/>
-      <c r="H23" s="7" t="n"/>
-    </row>
-    <row r="24" ht="32" customHeight="1">
-      <c r="A24" s="14" t="inlineStr">
-        <is>
-          <t>高</t>
-        </is>
-      </c>
-      <c r="B24" s="8" t="n">
-        <v>8</v>
-      </c>
-      <c r="C24" s="5" t="inlineStr">
-        <is>
-          <t>No.2 訪問系・通所系事業所の運営規程における通、No.3 令和6年・令和7年の町別住民基本台帳人口、No.5 保険者機能強化推進交付金等の評価調書（令、No.6 国民健康保険団体連合会の給付実績情報と指、No.7 事業所・施設の定員と稼働の実績、No.8 未利用認定者の内訳とケアプランのサービス、No.9 決算書及び介護給付費準備基金の積立・取崩、No.11 第10期の政令改正の内容（所得段階・乗率</t>
-        </is>
-      </c>
-      <c r="D24" s="23" t="n"/>
-      <c r="E24" s="23" t="n"/>
-      <c r="F24" s="23" t="n"/>
-      <c r="G24" s="23" t="n"/>
-      <c r="H24" s="7" t="n"/>
-    </row>
-    <row r="25" ht="32" customHeight="1">
-      <c r="A25" s="12" t="inlineStr">
-        <is>
-          <t>中</t>
-        </is>
-      </c>
-      <c r="B25" s="8" t="n">
-        <v>3</v>
-      </c>
-      <c r="C25" s="5" t="inlineStr">
-        <is>
-          <t>No.10 第7期（平成30〜令和2年度）の保険料条、No.12 小学校区と日常生活圏域の対応関係、No.15 第9期の自己評価と北海道への報告の実績</t>
-        </is>
-      </c>
-      <c r="D25" s="23" t="n"/>
-      <c r="E25" s="23" t="n"/>
-      <c r="F25" s="23" t="n"/>
-      <c r="G25" s="23" t="n"/>
-      <c r="H25" s="7" t="n"/>
-    </row>
-    <row r="26" ht="32" customHeight="1">
-      <c r="A26" s="24" t="inlineStr">
-        <is>
-          <t>低</t>
         </is>
       </c>
       <c r="B26" s="8" t="n">
@@ -5524,7 +5806,7 @@
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>No.1 見える化B5a・B6a・B6bの令和8年、No.4 令和7年国勢調査による町別の高齢者を含む</t>
+          <t>No.13 令和6〜8年度の施策・事業実績、事業量、、No.14 在宅生活改善調査・居所変更実態調査・介護</t>
         </is>
       </c>
       <c r="D26" s="23" t="n"/>
@@ -5533,23 +5815,83 @@
       <c r="G26" s="23" t="n"/>
       <c r="H26" s="7" t="n"/>
     </row>
-    <row r="28" ht="36" customHeight="1">
-      <c r="A28" s="17" t="inlineStr">
-        <is>
-          <t>注1）最高優先の2件（No.13 事業実績、No.14 3調査）は、いずれも業務内容そのものが進まない資料である。No.13がなければ第9期のプロセス評価ができず、No.14がなければ仕様書４（3）が完了しない。注2）高優先の8件は、いずれも成果物の主張の水準を推論（E4）・仮説（E5）から引き上げるために必要である。特にNo.6（国保連の給付実績情報と指定事業所台帳）は、給付水準の要因という第10期の中心論点を確定する唯一の手段である。注3）本表の資料は、業務工程管理表 03シートの確認事項と対応する。確認事項は決定を求めるもの、本表は資料の提供を求めるものである。</t>
+    <row r="27" ht="32" customHeight="1">
+      <c r="A27" s="14" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="B27" s="8" t="n">
+        <v>10</v>
+      </c>
+      <c r="C27" s="5" t="inlineStr">
+        <is>
+          <t>No.2 訪問系・通所系事業所の運営規程における通、No.3 令和6年・令和7年の町別住民基本台帳人口、No.5 保険者機能強化推進交付金等の評価調書（令、No.6 国民健康保険団体連合会の給付実績情報と指、No.7 事業所・施設の定員と稼働の実績、No.8 未利用認定者の内訳とケアプランのサービス、No.9 決算書及び介護給付費準備基金の積立・取崩、No.11 第10期の政令改正の内容（所得段階・乗率、No.17 町別・サービス区分別の給付費（令和4〜7、No.18 指定事業所台帳（区域外事業所の所在地）</t>
+        </is>
+      </c>
+      <c r="D27" s="23" t="n"/>
+      <c r="E27" s="23" t="n"/>
+      <c r="F27" s="23" t="n"/>
+      <c r="G27" s="23" t="n"/>
+      <c r="H27" s="7" t="n"/>
+    </row>
+    <row r="28" ht="32" customHeight="1">
+      <c r="A28" s="12" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="B28" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="C28" s="5" t="inlineStr">
+        <is>
+          <t>No.12 小学校区と日常生活圏域の対応関係、No.16 見える化システムD49の指標定義、No.15 第9期の自己評価と北海道への報告の実績</t>
+        </is>
+      </c>
+      <c r="D28" s="23" t="n"/>
+      <c r="E28" s="23" t="n"/>
+      <c r="F28" s="23" t="n"/>
+      <c r="G28" s="23" t="n"/>
+      <c r="H28" s="7" t="n"/>
+    </row>
+    <row r="29" ht="32" customHeight="1">
+      <c r="A29" s="24" t="inlineStr">
+        <is>
+          <t>低</t>
+        </is>
+      </c>
+      <c r="B29" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="C29" s="5" t="inlineStr">
+        <is>
+          <t>No.1 見える化B5a・B6a・B6bの令和8年、No.4 令和7年国勢調査による町別の高齢者を含む、No.10 第7期（平成30〜令和2年度）の保険料条</t>
+        </is>
+      </c>
+      <c r="D29" s="23" t="n"/>
+      <c r="E29" s="23" t="n"/>
+      <c r="F29" s="23" t="n"/>
+      <c r="G29" s="23" t="n"/>
+      <c r="H29" s="7" t="n"/>
+    </row>
+    <row r="31" ht="36" customHeight="1">
+      <c r="A31" s="17" t="inlineStr">
+        <is>
+          <t>注1）最高優先の2件（No.13 事業実績、No.14 3調査）は、いずれも業務内容そのものが進まない資料である。No.13がなければ第9期のプロセス評価ができず、No.14がなければ仕様書４（3）が完了しない。注2）高優先の10件は、いずれも成果物の主張の水準を推論（E4）・仮説（E5）から引き上げるために必要である。特にNo.6（国保連の給付実績情報と指定事業所台帳）は、給付水準の要因という第10期の中心論点を確定する唯一の手段である。注3）本表の資料は、業務工程管理表 03シートの確認事項と対応する。確認事項は決定を求めるもの、本表は資料の提供を求めるものである。</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="8">
-    <mergeCell ref="C25:H25"/>
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="C28:H28"/>
+    <mergeCell ref="C27:H27"/>
+    <mergeCell ref="A24:H24"/>
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A31:H31"/>
     <mergeCell ref="C26:H26"/>
-    <mergeCell ref="C24:H24"/>
-    <mergeCell ref="A21:H21"/>
-    <mergeCell ref="A2:H2"/>
-    <mergeCell ref="C23:H23"/>
-    <mergeCell ref="A28:H28"/>
-    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="C29:H29"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/第10期計画_主張の根拠水準の棚卸しと再レビュー.xlsx
+++ b/output/第10期計画_主張の根拠水準の棚卸しと再レビュー.xlsx
@@ -670,7 +670,7 @@
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>全成果物の主要な主張54件を、領域別・根拠水準別に分類する。記述の形（断定・留保付き断定・推量・記述せず）を併記する。</t>
+          <t>全成果物の主要な主張59件を、領域別・根拠水準別に分類する。記述の形（断定・留保付き断定・推量・記述せず）を併記する。</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
@@ -877,12 +877,12 @@
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>A1、A2、A3、A4</t>
+          <t>A1、A2、A3、A4、A5、A6、A7、A8、A9</t>
         </is>
       </c>
       <c r="D15" s="7" t="n"/>
       <c r="E15" s="8" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
     </row>
     <row r="16" ht="20" customHeight="1">
@@ -1122,7 +1122,7 @@
       </c>
       <c r="D28" s="7" t="n"/>
       <c r="E28" s="8" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="29" ht="32" customHeight="1">
@@ -1143,7 +1143,7 @@
       </c>
       <c r="D29" s="7" t="n"/>
       <c r="E29" s="8" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="30" ht="32" customHeight="1">
@@ -1164,7 +1164,7 @@
       </c>
       <c r="D30" s="7" t="n"/>
       <c r="E30" s="8" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="31" ht="32" customHeight="1">
@@ -1227,7 +1227,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G60"/>
+  <dimension ref="A1:G65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -1242,7 +1242,7 @@
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>主張の棚卸し（54件）</t>
+          <t>主張の棚卸し（59件）</t>
         </is>
       </c>
     </row>
@@ -1392,12 +1392,12 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>B4系列から逆算。合計認定率の上昇の主因であることを直接法で確認</t>
+          <t>B4系列から逆算。合計認定率の上昇の主因であることを直接法で確認。見える化A4（実数）により85歳以上人口を直接確認できるようになった（2019年1,907人→2025年2,167人）</t>
         </is>
       </c>
       <c r="G7" s="5" t="inlineStr">
         <is>
-          <t>逆算に丸め誤差を含む。認定率が小数第1位までの公表値であるため、人口の逆算値は±数十人の誤差がありうる</t>
+          <t>逆算に丸め誤差を含む。A4は各年10月1日現在、認定者数は3月末であり基準時点が異なる</t>
         </is>
       </c>
     </row>
@@ -1441,22 +1441,22 @@
     <row r="9" ht="52" customHeight="1">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>B1</t>
+          <t>A5</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>年齢構成を調整すると合計認定率は低下している</t>
-        </is>
-      </c>
-      <c r="D9" s="9" t="inlineStr">
-        <is>
-          <t>E2</t>
+          <t>第10期計画期間中、65歳以上人口はほぼ横ばいである（令和7年9,323人→令和11年9,313人・▲0.1％）</t>
+        </is>
+      </c>
+      <c r="D9" s="11" t="inlineStr">
+        <is>
+          <t>E3</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -1466,29 +1466,29 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>3階級による直接法（令和元年20.33％→令和8年19.69％）と見える化B5a（平成30年17.8％→令和7年16.7％）の2方法が一致</t>
+          <t>見える化A2（社人研推計・令和8年7月30日受領）</t>
         </is>
       </c>
       <c r="G9" s="5" t="inlineStr">
         <is>
-          <t>独立な2方法が一致しており確度は高い</t>
+          <t>総人口は▲3.3％であり、高齢化率の上昇（34.4％→35.6％）は分母の減少による。この点を必ず併記する</t>
         </is>
       </c>
     </row>
     <row r="10" ht="52" customHeight="1">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>B2</t>
+          <t>A6</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>65〜74歳の認定率は平成30年3.78％から令和8年4.03％へ上昇している</t>
+          <t>第10期計画期間中に増える年齢階級は80〜84歳と85歳以上のみである</t>
         </is>
       </c>
       <c r="D10" s="9" t="inlineStr">
@@ -1498,39 +1498,39 @@
       </c>
       <c r="E10" s="5" t="inlineStr">
         <is>
-          <t>断定（留保付き）</t>
+          <t>断定</t>
         </is>
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>B4a・B4c・B4dからの逆算</t>
+          <t>見える化A4から算定。令和7年→令和11年で80〜84歳＋282人・85歳以上＋89人、70〜74歳▲288人・75〜79歳▲183人</t>
         </is>
       </c>
       <c r="G10" s="5" t="inlineStr">
         <is>
-          <t>認定者数は158人から145人へ減少しており、率の上昇は人口の減少による。この留保を必ず併記する</t>
+          <t>認定率を年齢階級別に設定する根拠となる。A4は各年10月1日現在であり認定者数（3月末）と基準時点が異なる</t>
         </is>
       </c>
     </row>
     <row r="11" ht="52" customHeight="1">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>B3</t>
+          <t>A7</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>中重度は低下が続き、軽度は令和5年を底に上昇に転じている</t>
-        </is>
-      </c>
-      <c r="D11" s="9" t="inlineStr">
-        <is>
-          <t>E2</t>
+          <t>85歳以上人口は令和7年2,167人から令和22年2,810人へ29.7％増加する</t>
+        </is>
+      </c>
+      <c r="D11" s="11" t="inlineStr">
+        <is>
+          <t>E3</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -1540,108 +1540,108 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>見える化B6a（5.4％→4.7％）・B6b（11.7％→12.0％）</t>
+          <t>見える化A4</t>
         </is>
       </c>
       <c r="G11" s="5" t="inlineStr">
         <is>
-          <t>B6は令和7年3月末までであり、令和8年3月末の値がない（不足資料 No.1）</t>
+          <t>令和9年（2,212人）を起点とすると＋27.0％であり、従来の記述（令和9年度比で約27％増加）と整合する</t>
         </is>
       </c>
     </row>
     <row r="12" ht="52" customHeight="1">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>B4</t>
+          <t>A8</t>
         </is>
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>W144（性年齢調整済み要介護2以上認定率）の上昇の要因</t>
-        </is>
-      </c>
-      <c r="D12" s="15" t="inlineStr">
-        <is>
-          <t>E5</t>
+          <t>15〜64歳人口は令和2年15,099人から令和22年11,492人へ23.9％減少する</t>
+        </is>
+      </c>
+      <c r="D12" s="11" t="inlineStr">
+        <is>
+          <t>E3</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
-          <t>記述せず</t>
+          <t>断定</t>
         </is>
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
+          <t>見える化A9。高齢者1人あたりの現役世代は1.6人から1.2人となる</t>
+        </is>
+      </c>
+      <c r="G12" s="5" t="inlineStr">
+        <is>
           <t>―</t>
-        </is>
-      </c>
-      <c r="G12" s="5" t="inlineStr">
-        <is>
-          <t>現時点で説明できない。評価調書により分子・分母の実数を確認する（不足資料 No.5）。仮説を立てて記述しない</t>
         </is>
       </c>
     </row>
     <row r="13" ht="52" customHeight="1">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>B5</t>
+          <t>A9</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>第9期計画の高齢化率が低いのは分母（総人口）の過大が原因である</t>
+        </is>
+      </c>
+      <c r="D13" s="13" t="inlineStr">
+        <is>
+          <t>E4</t>
+        </is>
+      </c>
+      <c r="E13" s="5" t="inlineStr">
+        <is>
+          <t>撤回</t>
+        </is>
+      </c>
+      <c r="F13" s="5" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="G13" s="5" t="inlineStr">
+        <is>
+          <t>撤回した。令和5年の差1.10ポイントのうち分子（高齢者数）の寄与＋0.64ポイントが分母（総人口）の寄与＋0.46ポイントを上回る。レッドチームレビューNo.23の指摘が的中した（人口推計の基礎の検証04シート）</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="52" customHeight="1">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>B1</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
           <t>B</t>
         </is>
       </c>
-      <c r="C13" s="5" t="inlineStr">
-        <is>
-          <t>重度化の速度は全国並みに収束すると置く</t>
-        </is>
-      </c>
-      <c r="D13" s="15" t="inlineStr">
-        <is>
-          <t>E5</t>
-        </is>
-      </c>
-      <c r="E13" s="5" t="inlineStr">
-        <is>
-          <t>前提の選択として明示</t>
-        </is>
-      </c>
-      <c r="F13" s="5" t="inlineStr">
-        <is>
-          <t>―</t>
-        </is>
-      </c>
-      <c r="G13" s="5" t="inlineStr">
-        <is>
-          <t>推計の前提であり事実の主張ではない。選択肢と推奨を示し、発注者の決定を仰ぐ（確認事項No.29）</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="52" customHeight="1">
-      <c r="A14" s="15" t="inlineStr">
-        <is>
-          <t>C1</t>
-        </is>
-      </c>
-      <c r="B14" s="4" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>給付水準の高さは施設・居住系サービスの受給率と受給者単価がともに高いことによる</t>
-        </is>
-      </c>
-      <c r="D14" s="13" t="inlineStr">
-        <is>
-          <t>E4</t>
+          <t>年齢構成を調整すると合計認定率は低下している</t>
+        </is>
+      </c>
+      <c r="D14" s="9" t="inlineStr">
+        <is>
+          <t>E2</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -1651,219 +1651,219 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>見える化D49の4要素の水準（給付月額1.08・認定率1.02・受給率1.08・受給者単価1.06）。上川管内21保険者では給付月額指数の差を受給者単価が最もよく説明する（R²＝0.62）</t>
+          <t>3階級による直接法（令和元年20.33％→令和8年19.69％）と見える化B5a（平成30年17.8％→令和7年16.7％）の2方法が一致</t>
         </is>
       </c>
       <c r="G14" s="5" t="inlineStr">
         <is>
-          <t>3要素は独立ではない（受給率と単価はr＝0.873）。さらに受給率×単価は給付月額指数に一致しない（大雪＋0.065、管内16/21で0.03超）。指数の分解による按分は撤回した（地域差の分析04・05シート）</t>
+          <t>独立な2方法が一致しており確度は高い</t>
         </is>
       </c>
     </row>
     <row r="15" ht="52" customHeight="1">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>C2</t>
+          <t>B2</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>施設・居住系の受給率は在宅より全国比が高い（1.23対1.02）</t>
-        </is>
-      </c>
-      <c r="D15" s="11" t="inlineStr">
-        <is>
-          <t>E3</t>
+          <t>65〜74歳の認定率は平成30年3.78％から令和8年4.03％へ上昇している</t>
+        </is>
+      </c>
+      <c r="D15" s="9" t="inlineStr">
+        <is>
+          <t>E2</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
         <is>
+          <t>断定（留保付き）</t>
+        </is>
+      </c>
+      <c r="F15" s="5" t="inlineStr">
+        <is>
+          <t>B4a・B4c・B4dからの逆算</t>
+        </is>
+      </c>
+      <c r="G15" s="5" t="inlineStr">
+        <is>
+          <t>認定者数は158人から145人へ減少しており、率の上昇は人口の減少による。この留保を必ず併記する</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="52" customHeight="1">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>B3</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>中重度は低下が続き、軽度は令和5年を底に上昇に転じている</t>
+        </is>
+      </c>
+      <c r="D16" s="9" t="inlineStr">
+        <is>
+          <t>E2</t>
+        </is>
+      </c>
+      <c r="E16" s="5" t="inlineStr">
+        <is>
           <t>断定</t>
         </is>
       </c>
-      <c r="F15" s="5" t="inlineStr">
-        <is>
-          <t>見える化D41の受給率</t>
-        </is>
-      </c>
-      <c r="G15" s="5" t="inlineStr">
-        <is>
-          <t>受給率の水準の対比としては確定している。超過分を要素別に按分する記述は撤回した（地域差の分析05シート）</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="52" customHeight="1">
-      <c r="A16" s="15" t="inlineStr">
-        <is>
-          <t>C3</t>
-        </is>
-      </c>
-      <c r="B16" s="4" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="C16" s="5" t="inlineStr">
-        <is>
-          <t>受給率の低下分のほぼ全てが要介護5に由来する</t>
-        </is>
-      </c>
-      <c r="D16" s="13" t="inlineStr">
-        <is>
-          <t>E4</t>
-        </is>
-      </c>
-      <c r="E16" s="5" t="inlineStr">
-        <is>
-          <t>断定</t>
-        </is>
-      </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>見える化D41-aの要介護度別受給率の推移</t>
+          <t>見える化B6a（5.4％→4.7％）・B6b（11.7％→12.0％）</t>
         </is>
       </c>
       <c r="G16" s="5" t="inlineStr">
         <is>
-          <t>要介護5の受給者が減った理由（死亡・施設入所・認定の変化）を特定していない。「低下分の大半は要介護5の受給率の低下による」に改める</t>
+          <t>B6は令和7年3月末までであり、令和8年3月末の値がない（不足資料 No.1）</t>
         </is>
       </c>
     </row>
     <row r="17" ht="52" customHeight="1">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>C4</t>
+          <t>B4</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>訪問介護の利用回数は全国の1.87倍、通所介護の受給者単価は全国の0.74倍</t>
-        </is>
-      </c>
-      <c r="D17" s="11" t="inlineStr">
-        <is>
-          <t>E3</t>
+          <t>W144（性年齢調整済み要介護2以上認定率）の上昇の要因</t>
+        </is>
+      </c>
+      <c r="D17" s="15" t="inlineStr">
+        <is>
+          <t>E5</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
-          <t>断定</t>
+          <t>記述せず</t>
         </is>
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>見える化D31（令和7年）</t>
+          <t>―</t>
         </is>
       </c>
       <c r="G17" s="5" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>現時点で説明できない。評価調書により分子・分母の実数を確認する（不足資料 No.5）。仮説を立てて記述しない</t>
         </is>
       </c>
     </row>
     <row r="18" ht="52" customHeight="1">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>C5</t>
+          <t>B5</t>
         </is>
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>重度化の速度は全国並みに収束すると置く</t>
+        </is>
+      </c>
+      <c r="D18" s="15" t="inlineStr">
+        <is>
+          <t>E5</t>
+        </is>
+      </c>
+      <c r="E18" s="5" t="inlineStr">
+        <is>
+          <t>前提の選択として明示</t>
+        </is>
+      </c>
+      <c r="F18" s="5" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="G18" s="5" t="inlineStr">
+        <is>
+          <t>推計の前提であり事実の主張ではない。選択肢と推奨を示し、発注者の決定を仰ぐ（確認事項No.29）</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="52" customHeight="1">
+      <c r="A19" s="15" t="inlineStr">
+        <is>
+          <t>C1</t>
+        </is>
+      </c>
+      <c r="B19" s="4" t="inlineStr">
+        <is>
           <t>C</t>
         </is>
       </c>
-      <c r="C18" s="5" t="inlineStr">
-        <is>
-          <t>給付費の増加は在宅サービスが牽引している</t>
-        </is>
-      </c>
-      <c r="D18" s="9" t="inlineStr">
-        <is>
-          <t>E2</t>
-        </is>
-      </c>
-      <c r="E18" s="5" t="inlineStr">
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>給付水準の高さは施設・居住系サービスの受給率と受給者単価がともに高いことによる</t>
+        </is>
+      </c>
+      <c r="D19" s="13" t="inlineStr">
+        <is>
+          <t>E4</t>
+        </is>
+      </c>
+      <c r="E19" s="5" t="inlineStr">
         <is>
           <t>断定</t>
         </is>
       </c>
-      <c r="F18" s="5" t="inlineStr">
-        <is>
-          <t>見える化P4の必要保険料内訳（在宅2,156円→2,596円で＋20.4％）</t>
-        </is>
-      </c>
-      <c r="G18" s="5" t="inlineStr">
-        <is>
-          <t>―</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="52" customHeight="1">
-      <c r="A19" s="4" t="inlineStr">
-        <is>
-          <t>D1</t>
-        </is>
-      </c>
-      <c r="B19" s="4" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="C19" s="5" t="inlineStr">
-        <is>
-          <t>全28サービス種別のうち11種別で区域内に事業所が存在しない</t>
-        </is>
-      </c>
-      <c r="D19" s="9" t="inlineStr">
-        <is>
-          <t>E2</t>
-        </is>
-      </c>
-      <c r="E19" s="5" t="inlineStr">
-        <is>
-          <t>断定</t>
-        </is>
-      </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>見える化K1・K2・K3系列の全年次を確認</t>
+          <t>見える化D49の4要素の水準（給付月額1.08・認定率1.02・受給率1.08・受給者単価1.06）。上川管内21保険者では給付月額指数の差を受給者単価が最もよく説明する（R²＝0.62）</t>
         </is>
       </c>
       <c r="G19" s="5" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>3要素は独立ではない（受給率と単価はr＝0.873）。さらに受給率×単価は給付月額指数に一致しない（大雪＋0.065、管内16/21で0.03超）。指数の分解による按分は撤回した（地域差の分析04・05シート）</t>
         </is>
       </c>
     </row>
     <row r="20" ht="52" customHeight="1">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>D2</t>
+          <t>C2</t>
         </is>
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>24時間対応の3サービスは制度創設以来13年間ゼロである</t>
-        </is>
-      </c>
-      <c r="D20" s="9" t="inlineStr">
-        <is>
-          <t>E2</t>
+          <t>施設・居住系の受給率は在宅より全国比が高い（1.23対1.02）</t>
+        </is>
+      </c>
+      <c r="D20" s="11" t="inlineStr">
+        <is>
+          <t>E3</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
@@ -1873,34 +1873,34 @@
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>K3m・K3n・K3qの平成24年度〜令和6年度の全年次がゼロ</t>
+          <t>見える化D41の受給率</t>
         </is>
       </c>
       <c r="G20" s="5" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>受給率の水準の対比としては確定している。超過分を要素別に按分する記述は撤回した（地域差の分析05シート）</t>
         </is>
       </c>
     </row>
     <row r="21" ht="52" customHeight="1">
       <c r="A21" s="15" t="inlineStr">
         <is>
-          <t>D3</t>
+          <t>C3</t>
         </is>
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>地域密着型通所介護の給付減は稼働率の低下によるものである</t>
-        </is>
-      </c>
-      <c r="D21" s="15" t="inlineStr">
-        <is>
-          <t>E5</t>
+          <t>受給率の低下分のほぼ全てが要介護5に由来する</t>
+        </is>
+      </c>
+      <c r="D21" s="13" t="inlineStr">
+        <is>
+          <t>E4</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
@@ -1910,29 +1910,29 @@
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>事業所数4で不変、従事者は増加、給付費は27.0％減という3系列の組合せ</t>
+          <t>見える化D41-aの要介護度別受給率の推移</t>
         </is>
       </c>
       <c r="G21" s="5" t="inlineStr">
         <is>
-          <t>稼働率そのものを確認していない。定員・登録者数・延べ利用者数が未受領（不足資料 No.7）。「稼働率の低下が疑われる」に改める</t>
+          <t>要介護5の受給者が減った理由（死亡・施設入所・認定の変化）を特定していない。「低下分の大半は要介護5の受給率の低下による」に改める</t>
         </is>
       </c>
     </row>
     <row r="22" ht="52" customHeight="1">
       <c r="A22" s="4" t="inlineStr">
         <is>
-          <t>D4</t>
+          <t>C4</t>
         </is>
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>介護老人福祉施設の定員が234人から160人へ減少している</t>
+          <t>訪問介護の利用回数は全国の1.87倍、通所介護の受給者単価は全国の0.74倍</t>
         </is>
       </c>
       <c r="D22" s="11" t="inlineStr">
@@ -1947,29 +1947,29 @@
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>見える化D25（平成29年度・令和2年度以降）</t>
+          <t>見える化D31（令和7年）</t>
         </is>
       </c>
       <c r="G22" s="5" t="inlineStr">
         <is>
-          <t>減少の経緯（休廃止・転換・休止床の整理）を確認していない。実稼働の定員が減っていない可能性がある（不足資料 No.7）</t>
+          <t>―</t>
         </is>
       </c>
     </row>
     <row r="23" ht="52" customHeight="1">
       <c r="A23" s="4" t="inlineStr">
         <is>
-          <t>D5</t>
+          <t>C5</t>
         </is>
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>施設・居住系の給付のうち区域外の事業所によるものは東川町23.2％・美瑛町24.7％・東神楽町34.5％である</t>
+          <t>給付費の増加は在宅サービスが牽引している</t>
         </is>
       </c>
       <c r="D23" s="9" t="inlineStr">
@@ -1984,34 +1984,34 @@
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>見える化δ（介護サービス自給率・令和7年9月。令和8年7月30日受領）</t>
+          <t>見える化P4の必要保険料内訳（在宅2,156円→2,596円で＋20.4％）</t>
         </is>
       </c>
       <c r="G23" s="5" t="inlineStr">
         <is>
-          <t>確定。定員が減少しても受給が維持されている背景が説明できた。ただし区域外利用が給付水準の高さの原因であるという部分は関係が確認できず（管内15件でr＝0.07）、記述しない</t>
+          <t>―</t>
         </is>
       </c>
     </row>
     <row r="24" ht="52" customHeight="1">
       <c r="A24" s="4" t="inlineStr">
         <is>
-          <t>E1</t>
+          <t>D1</t>
         </is>
       </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>D</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>介護サービス利用率が平成28年度82.2％から令和6年度74.3％へ低下している</t>
-        </is>
-      </c>
-      <c r="D24" s="11" t="inlineStr">
-        <is>
-          <t>E3</t>
+          <t>全28サービス種別のうち11種別で区域内に事業所が存在しない</t>
+        </is>
+      </c>
+      <c r="D24" s="9" t="inlineStr">
+        <is>
+          <t>E2</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">
@@ -2021,7 +2021,7 @@
       </c>
       <c r="F24" s="5" t="inlineStr">
         <is>
-          <t>見える化D42</t>
+          <t>見える化K1・K2・K3系列の全年次を確認</t>
         </is>
       </c>
       <c r="G24" s="5" t="inlineStr">
@@ -2033,24 +2033,24 @@
     <row r="25" ht="52" customHeight="1">
       <c r="A25" s="4" t="inlineStr">
         <is>
+          <t>D2</t>
+        </is>
+      </c>
+      <c r="B25" s="4" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>24時間対応の3サービスは制度創設以来13年間ゼロである</t>
+        </is>
+      </c>
+      <c r="D25" s="9" t="inlineStr">
+        <is>
           <t>E2</t>
         </is>
       </c>
-      <c r="B25" s="4" t="inlineStr">
-        <is>
-          <t>E</t>
-        </is>
-      </c>
-      <c r="C25" s="5" t="inlineStr">
-        <is>
-          <t>令和6年度の未利用認定者は504人（認定者の25.7％）である</t>
-        </is>
-      </c>
-      <c r="D25" s="9" t="inlineStr">
-        <is>
-          <t>E2</t>
-        </is>
-      </c>
       <c r="E25" s="5" t="inlineStr">
         <is>
           <t>断定</t>
@@ -2058,29 +2058,29 @@
       </c>
       <c r="F25" s="5" t="inlineStr">
         <is>
-          <t>認定者1,962人と受給者1,458人の差として算定</t>
+          <t>K3m・K3n・K3qの平成24年度〜令和6年度の全年次がゼロ</t>
         </is>
       </c>
       <c r="G25" s="5" t="inlineStr">
         <is>
-          <t>月平均と年度末で母数が異なる可能性がある。基準時点を明記する</t>
+          <t>―</t>
         </is>
       </c>
     </row>
     <row r="26" ht="52" customHeight="1">
-      <c r="A26" s="4" t="inlineStr">
-        <is>
-          <t>E3</t>
+      <c r="A26" s="15" t="inlineStr">
+        <is>
+          <t>D3</t>
         </is>
       </c>
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>D</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>利用率低下の要因</t>
+          <t>地域密着型通所介護の給付減は稼働率の低下によるものである</t>
         </is>
       </c>
       <c r="D26" s="15" t="inlineStr">
@@ -2090,71 +2090,71 @@
       </c>
       <c r="E26" s="5" t="inlineStr">
         <is>
-          <t>特定しない旨を明示</t>
+          <t>断定</t>
         </is>
       </c>
       <c r="F26" s="5" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>事業所数4で不変、従事者は増加、給付費は27.0％減という3系列の組合せ</t>
         </is>
       </c>
       <c r="G26" s="5" t="inlineStr">
         <is>
-          <t>軽度で自立・申請先行・家族介護・経済的理由・供給制約が並立する。要因の分解を第10期の課題として位置づける（不足資料 No.8）</t>
+          <t>稼働率そのものを確認していない。定員・登録者数・延べ利用者数が未受領（不足資料 No.7）。「稼働率の低下が疑われる」に改める</t>
         </is>
       </c>
     </row>
     <row r="27" ht="52" customHeight="1">
       <c r="A27" s="4" t="inlineStr">
         <is>
-          <t>E4</t>
+          <t>D4</t>
         </is>
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>D</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>訪問介護の高い利用強度は通所の供給が薄いことによる代替である</t>
-        </is>
-      </c>
-      <c r="D27" s="15" t="inlineStr">
-        <is>
-          <t>E5</t>
+          <t>介護老人福祉施設の定員が234人から160人へ減少している</t>
+        </is>
+      </c>
+      <c r="D27" s="11" t="inlineStr">
+        <is>
+          <t>E3</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr">
         <is>
-          <t>推量で記述</t>
+          <t>断定</t>
         </is>
       </c>
       <c r="F27" s="5" t="inlineStr">
         <is>
-          <t>訪問介護1.87倍と通所0.74倍という2つの比率の対比</t>
+          <t>見える化D25（平成29年度・令和2年度以降）</t>
         </is>
       </c>
       <c r="G27" s="5" t="inlineStr">
         <is>
-          <t>代替関係を検証していない。同一利用者の組合せを見ていない。ケアプランのサービス構成の確認を要する（不足資料 No.8）</t>
+          <t>減少の経緯（休廃止・転換・休止床の整理）を確認していない。実稼働の定員が減っていない可能性がある（不足資料 No.7）</t>
         </is>
       </c>
     </row>
     <row r="28" ht="52" customHeight="1">
       <c r="A28" s="4" t="inlineStr">
         <is>
-          <t>F1</t>
+          <t>D5</t>
         </is>
       </c>
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>D</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>通いの場参加率8.8％は同規模保険者13.2％の3分の2である</t>
+          <t>施設・居住系の給付のうち区域外の事業所によるものは東川町23.2％・美瑛町24.7％・東神楽町34.5％である</t>
         </is>
       </c>
       <c r="D28" s="9" t="inlineStr">
@@ -2169,34 +2169,34 @@
       </c>
       <c r="F28" s="5" t="inlineStr">
         <is>
-          <t>個票データから算定し調査報告書の公表値と完全一致。同規模保険者値は報告書</t>
+          <t>見える化δ（介護サービス自給率・令和7年9月。令和8年7月30日受領）</t>
         </is>
       </c>
       <c r="G28" s="5" t="inlineStr">
         <is>
-          <t>同規模保険者40のうち31は要支援者を調査対象に含むため、当広域連合の値は良好側へ偏る。この偏りがあってもなお低い</t>
+          <t>確定。定員が減少しても受給が維持されている背景が説明できた。ただし区域外利用が給付水準の高さの原因であるという部分は関係が確認できず（管内15件でr＝0.07）、記述しない</t>
         </is>
       </c>
     </row>
     <row r="29" ht="52" customHeight="1">
       <c r="A29" s="4" t="inlineStr">
         <is>
-          <t>F2</t>
+          <t>E1</t>
         </is>
       </c>
       <c r="B29" s="4" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>E</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>通いの場参加は男性3.8％・女性13.3％で3.5倍の差がある</t>
-        </is>
-      </c>
-      <c r="D29" s="9" t="inlineStr">
-        <is>
-          <t>E2</t>
+          <t>介護サービス利用率が平成28年度82.2％から令和6年度74.3％へ低下している</t>
+        </is>
+      </c>
+      <c r="D29" s="11" t="inlineStr">
+        <is>
+          <t>E3</t>
         </is>
       </c>
       <c r="E29" s="5" t="inlineStr">
@@ -2206,7 +2206,7 @@
       </c>
       <c r="F29" s="5" t="inlineStr">
         <is>
-          <t>個票データから算定</t>
+          <t>見える化D42</t>
         </is>
       </c>
       <c r="G29" s="5" t="inlineStr">
@@ -2218,17 +2218,17 @@
     <row r="30" ht="52" customHeight="1">
       <c r="A30" s="4" t="inlineStr">
         <is>
-          <t>F3</t>
+          <t>E2</t>
         </is>
       </c>
       <c r="B30" s="4" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>E</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>社会参加のある層はリスク指標が良好である</t>
+          <t>令和6年度の未利用認定者は504人（認定者の25.7％）である</t>
         </is>
       </c>
       <c r="D30" s="9" t="inlineStr">
@@ -2238,98 +2238,98 @@
       </c>
       <c r="E30" s="5" t="inlineStr">
         <is>
-          <t>関連として記述</t>
+          <t>断定</t>
         </is>
       </c>
       <c r="F30" s="5" t="inlineStr">
         <is>
-          <t>個票データから算定。年齢階級で層化しても同じ方向</t>
+          <t>認定者1,962人と受給者1,458人の差として算定</t>
         </is>
       </c>
       <c r="G30" s="5" t="inlineStr">
         <is>
-          <t>横断調査であり因果ではない。逆方向の関係（状態が良いから参加できる）を併記している</t>
+          <t>月平均と年度末で母数が異なる可能性がある。基準時点を明記する</t>
         </is>
       </c>
     </row>
     <row r="31" ht="52" customHeight="1">
-      <c r="A31" s="15" t="inlineStr">
-        <is>
-          <t>F4</t>
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>E3</t>
         </is>
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>E</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>施設入所志向は心身の状態や経済状況ではなく支え手の有無で決まる</t>
-        </is>
-      </c>
-      <c r="D31" s="13" t="inlineStr">
-        <is>
-          <t>E4</t>
+          <t>利用率低下の要因</t>
+        </is>
+      </c>
+      <c r="D31" s="15" t="inlineStr">
+        <is>
+          <t>E5</t>
         </is>
       </c>
       <c r="E31" s="5" t="inlineStr">
         <is>
-          <t>断定</t>
+          <t>特定しない旨を明示</t>
         </is>
       </c>
       <c r="F31" s="5" t="inlineStr">
         <is>
-          <t>施設志向群と在宅志向群で困りごと・移動制約・経済状況・フレイルに有意差がなく、独居と支援者不在にのみ有意差がある</t>
+          <t>―</t>
         </is>
       </c>
       <c r="G31" s="5" t="inlineStr">
         <is>
-          <t>「差がない」ことは「関係がない」ことを意味しない。標本規模による検出力の問題を検討していない。「支え手の有無と結びついている」に改める</t>
+          <t>軽度で自立・申請先行・家族介護・経済的理由・供給制約が並立する。要因の分解を第10期の課題として位置づける（不足資料 No.8）</t>
         </is>
       </c>
     </row>
     <row r="32" ht="52" customHeight="1">
       <c r="A32" s="4" t="inlineStr">
         <is>
-          <t>F5</t>
+          <t>E4</t>
         </is>
       </c>
       <c r="B32" s="4" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>E</t>
         </is>
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>健康とくらしの調査の対象者は要支援者・要介護者を含まない</t>
-        </is>
-      </c>
-      <c r="D32" s="9" t="inlineStr">
-        <is>
-          <t>E1</t>
+          <t>訪問介護の高い利用強度は通所の供給が薄いことによる代替である</t>
+        </is>
+      </c>
+      <c r="D32" s="15" t="inlineStr">
+        <is>
+          <t>E5</t>
         </is>
       </c>
       <c r="E32" s="5" t="inlineStr">
         <is>
-          <t>断定</t>
+          <t>推量で記述</t>
         </is>
       </c>
       <c r="F32" s="5" t="inlineStr">
         <is>
-          <t>調査報告書「４（5）各保険者の調査対象者」の直接確認</t>
+          <t>訪問介護1.87倍と通所0.74倍という2つの比率の対比</t>
         </is>
       </c>
       <c r="G32" s="5" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>代替関係を検証していない。同一利用者の組合せを見ていない。ケアプランのサービス構成の確認を要する（不足資料 No.8）</t>
         </is>
       </c>
     </row>
     <row r="33" ht="52" customHeight="1">
       <c r="A33" s="4" t="inlineStr">
         <is>
-          <t>F6</t>
+          <t>F1</t>
         </is>
       </c>
       <c r="B33" s="4" t="inlineStr">
@@ -2339,7 +2339,7 @@
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>生活動作の困りごとの最上位は除雪である</t>
+          <t>通いの場参加率8.8％は同規模保険者13.2％の3分の2である</t>
         </is>
       </c>
       <c r="D33" s="9" t="inlineStr">
@@ -2354,34 +2354,34 @@
       </c>
       <c r="F33" s="5" t="inlineStr">
         <is>
-          <t>個票データから算定（24.3％）</t>
+          <t>個票データから算定し調査報告書の公表値と完全一致。同規模保険者値は報告書</t>
         </is>
       </c>
       <c r="G33" s="5" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>同規模保険者40のうち31は要支援者を調査対象に含むため、当広域連合の値は良好側へ偏る。この偏りがあってもなお低い</t>
         </is>
       </c>
     </row>
     <row r="34" ht="52" customHeight="1">
       <c r="A34" s="4" t="inlineStr">
         <is>
-          <t>G1</t>
+          <t>F2</t>
         </is>
       </c>
       <c r="B34" s="4" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>F</t>
         </is>
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t>交付金の総合得点332.0点は全国平均422.4点の78.6％である</t>
-        </is>
-      </c>
-      <c r="D34" s="11" t="inlineStr">
-        <is>
-          <t>E3</t>
+          <t>通いの場参加は男性3.8％・女性13.3％で3.5倍の差がある</t>
+        </is>
+      </c>
+      <c r="D34" s="9" t="inlineStr">
+        <is>
+          <t>E2</t>
         </is>
       </c>
       <c r="E34" s="5" t="inlineStr">
@@ -2391,7 +2391,7 @@
       </c>
       <c r="F34" s="5" t="inlineStr">
         <is>
-          <t>見える化W126</t>
+          <t>個票データから算定</t>
         </is>
       </c>
       <c r="G34" s="5" t="inlineStr">
@@ -2403,54 +2403,54 @@
     <row r="35" ht="52" customHeight="1">
       <c r="A35" s="4" t="inlineStr">
         <is>
-          <t>G2</t>
+          <t>F3</t>
         </is>
       </c>
       <c r="B35" s="4" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>F</t>
         </is>
       </c>
       <c r="C35" s="5" t="inlineStr">
         <is>
-          <t>活動指標群の得点は全国の23.2％にとどまる</t>
-        </is>
-      </c>
-      <c r="D35" s="11" t="inlineStr">
-        <is>
-          <t>E3</t>
+          <t>社会参加のある層はリスク指標が良好である</t>
+        </is>
+      </c>
+      <c r="D35" s="9" t="inlineStr">
+        <is>
+          <t>E2</t>
         </is>
       </c>
       <c r="E35" s="5" t="inlineStr">
         <is>
-          <t>断定</t>
+          <t>関連として記述</t>
         </is>
       </c>
       <c r="F35" s="5" t="inlineStr">
         <is>
-          <t>見える化W130</t>
+          <t>個票データから算定。年齢階級で層化しても同じ方向</t>
         </is>
       </c>
       <c r="G35" s="5" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>横断調査であり因果ではない。逆方向の関係（状態が良いから参加できる）を併記している</t>
         </is>
       </c>
     </row>
     <row r="36" ht="52" customHeight="1">
       <c r="A36" s="15" t="inlineStr">
         <is>
-          <t>G3</t>
+          <t>F4</t>
         </is>
       </c>
       <c r="B36" s="4" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>F</t>
         </is>
       </c>
       <c r="C36" s="5" t="inlineStr">
         <is>
-          <t>令和5年調査の交付金得点は第8期の取組を反映している</t>
+          <t>施設入所志向は心身の状態や経済状況ではなく支え手の有無で決まる</t>
         </is>
       </c>
       <c r="D36" s="13" t="inlineStr">
@@ -2465,34 +2465,34 @@
       </c>
       <c r="F36" s="5" t="inlineStr">
         <is>
-          <t>調査の実施年度と交付年度の関係からの推論</t>
+          <t>施設志向群と在宅志向群で困りごと・移動制約・経済状況・フレイルに有意差がなく、独居と支援者不在にのみ有意差がある</t>
         </is>
       </c>
       <c r="G36" s="5" t="inlineStr">
         <is>
-          <t>調査要領で評価対象期間を直接確認していない。「令和5年度に実施された調査であり、第9期（令和6年度〜）の取組は反映されていない」という限定に改める（不足資料 No.5）</t>
+          <t>「差がない」ことは「関係がない」ことを意味しない。標本規模による検出力の問題を検討していない。「支え手の有無と結びついている」に改める</t>
         </is>
       </c>
     </row>
     <row r="37" ht="52" customHeight="1">
       <c r="A37" s="4" t="inlineStr">
         <is>
-          <t>G4</t>
+          <t>F5</t>
         </is>
       </c>
       <c r="B37" s="4" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>F</t>
         </is>
       </c>
       <c r="C37" s="5" t="inlineStr">
         <is>
-          <t>数値目標を設定しているのは東川町のみである</t>
+          <t>健康とくらしの調査の対象者は要支援者・要介護者を含まない</t>
         </is>
       </c>
       <c r="D37" s="9" t="inlineStr">
         <is>
-          <t>E2</t>
+          <t>E1</t>
         </is>
       </c>
       <c r="E37" s="5" t="inlineStr">
@@ -2502,56 +2502,56 @@
       </c>
       <c r="F37" s="5" t="inlineStr">
         <is>
-          <t>3町の計画を各章にわたり目視で確認</t>
+          <t>調査報告書「４（5）各保険者の調査対象者」の直接確認</t>
         </is>
       </c>
       <c r="G37" s="5" t="inlineStr">
         <is>
-          <t>訂正済み。当初は全文検索により「3町とも設定なし」としていた</t>
+          <t>―</t>
         </is>
       </c>
     </row>
     <row r="38" ht="52" customHeight="1">
       <c r="A38" s="4" t="inlineStr">
         <is>
-          <t>G5</t>
+          <t>F6</t>
         </is>
       </c>
       <c r="B38" s="4" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>F</t>
         </is>
       </c>
       <c r="C38" s="5" t="inlineStr">
         <is>
-          <t>交付金の成果指標の統計的な安定性</t>
-        </is>
-      </c>
-      <c r="D38" s="15" t="inlineStr">
-        <is>
-          <t>E5</t>
+          <t>生活動作の困りごとの最上位は除雪である</t>
+        </is>
+      </c>
+      <c r="D38" s="9" t="inlineStr">
+        <is>
+          <t>E2</t>
         </is>
       </c>
       <c r="E38" s="5" t="inlineStr">
         <is>
-          <t>記述せず</t>
+          <t>断定</t>
         </is>
       </c>
       <c r="F38" s="5" t="inlineStr">
         <is>
+          <t>個票データから算定（24.3％）</t>
+        </is>
+      </c>
+      <c r="G38" s="5" t="inlineStr">
+        <is>
           <t>―</t>
-        </is>
-      </c>
-      <c r="G38" s="5" t="inlineStr">
-        <is>
-          <t>分子・分母の実数が未確認。「全国トップ級」等の表現を用いない（不足資料 No.5）</t>
         </is>
       </c>
     </row>
     <row r="39" ht="52" customHeight="1">
       <c r="A39" s="4" t="inlineStr">
         <is>
-          <t>G6</t>
+          <t>G1</t>
         </is>
       </c>
       <c r="B39" s="4" t="inlineStr">
@@ -2561,12 +2561,12 @@
       </c>
       <c r="C39" s="5" t="inlineStr">
         <is>
-          <t>第9期の19施策のうち13施策は計画記載上の評価可能性が低い</t>
-        </is>
-      </c>
-      <c r="D39" s="9" t="inlineStr">
-        <is>
-          <t>E2</t>
+          <t>交付金の総合得点332.0点は全国平均422.4点の78.6％である</t>
+        </is>
+      </c>
+      <c r="D39" s="11" t="inlineStr">
+        <is>
+          <t>E3</t>
         </is>
       </c>
       <c r="E39" s="5" t="inlineStr">
@@ -2576,34 +2576,34 @@
       </c>
       <c r="F39" s="5" t="inlineStr">
         <is>
-          <t>第9期計画 第5章の記載を確認</t>
+          <t>見える化W126</t>
         </is>
       </c>
       <c r="G39" s="5" t="inlineStr">
         <is>
-          <t>計画の記載の判定であり、施策の良否ではないことを明記済み</t>
+          <t>―</t>
         </is>
       </c>
     </row>
     <row r="40" ht="52" customHeight="1">
       <c r="A40" s="4" t="inlineStr">
         <is>
-          <t>H1</t>
+          <t>G2</t>
         </is>
       </c>
       <c r="B40" s="4" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>G</t>
         </is>
       </c>
       <c r="C40" s="5" t="inlineStr">
         <is>
-          <t>第9期の補正後被保険者数26,871人・算定上の基準額6,428円を再現できる</t>
-        </is>
-      </c>
-      <c r="D40" s="9" t="inlineStr">
-        <is>
-          <t>E2</t>
+          <t>活動指標群の得点は全国の23.2％にとどまる</t>
+        </is>
+      </c>
+      <c r="D40" s="11" t="inlineStr">
+        <is>
+          <t>E3</t>
         </is>
       </c>
       <c r="E40" s="5" t="inlineStr">
@@ -2613,7 +2613,7 @@
       </c>
       <c r="F40" s="5" t="inlineStr">
         <is>
-          <t>段階別被保険者数×公費軽減前の乗率の合計が公表値と完全一致</t>
+          <t>見える化W130</t>
         </is>
       </c>
       <c r="G40" s="5" t="inlineStr">
@@ -2623,56 +2623,56 @@
       </c>
     </row>
     <row r="41" ht="52" customHeight="1">
-      <c r="A41" s="4" t="inlineStr">
-        <is>
-          <t>H2</t>
+      <c r="A41" s="15" t="inlineStr">
+        <is>
+          <t>G3</t>
         </is>
       </c>
       <c r="B41" s="4" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>G</t>
         </is>
       </c>
       <c r="C41" s="5" t="inlineStr">
         <is>
-          <t>16段階の設定により保険料基準額は国標準13段階の場合より月52円低い</t>
-        </is>
-      </c>
-      <c r="D41" s="9" t="inlineStr">
-        <is>
-          <t>E2</t>
+          <t>令和5年調査の交付金得点は第8期の取組を反映している</t>
+        </is>
+      </c>
+      <c r="D41" s="13" t="inlineStr">
+        <is>
+          <t>E4</t>
         </is>
       </c>
       <c r="E41" s="5" t="inlineStr">
         <is>
-          <t>断定（試算）</t>
+          <t>断定</t>
         </is>
       </c>
       <c r="F41" s="5" t="inlineStr">
         <is>
-          <t>本表の試算（乗率のみを置換）</t>
+          <t>調査の実施年度と交付年度の関係からの推論</t>
         </is>
       </c>
       <c r="G41" s="5" t="inlineStr">
         <is>
-          <t>段階の区分そのものも異なるため概算である旨を明記済み</t>
+          <t>調査要領で評価対象期間を直接確認していない。「令和5年度に実施された調査であり、第9期（令和6年度〜）の取組は反映されていない」という限定に改める（不足資料 No.5）</t>
         </is>
       </c>
     </row>
     <row r="42" ht="52" customHeight="1">
       <c r="A42" s="4" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>G4</t>
         </is>
       </c>
       <c r="B42" s="4" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>G</t>
         </is>
       </c>
       <c r="C42" s="5" t="inlineStr">
         <is>
-          <t>第9期は2年で約42百万円の剰余が生じている</t>
+          <t>数値目標を設定しているのは東川町のみである</t>
         </is>
       </c>
       <c r="D42" s="9" t="inlineStr">
@@ -2682,76 +2682,76 @@
       </c>
       <c r="E42" s="5" t="inlineStr">
         <is>
-          <t>断定（概算と明記）</t>
+          <t>断定</t>
         </is>
       </c>
       <c r="F42" s="5" t="inlineStr">
         <is>
-          <t>見える化C1により令和6年度＋337円・令和7年度＋48円（累計385円／月）を確認。被保険者数約9,190人により金額換算</t>
+          <t>3町の計画を各章にわたり目視で確認</t>
         </is>
       </c>
       <c r="G42" s="5" t="inlineStr">
         <is>
-          <t>月額の差は原典で確定した。金額換算は被保険者数の前提を含む。基金への積立実績との一致は未確認（不足資料 No.9）。令和6・7年度は年度途中までの集計である</t>
+          <t>訂正済み。当初は全文検索により「3町とも設定なし」としていた</t>
         </is>
       </c>
     </row>
     <row r="43" ht="52" customHeight="1">
       <c r="A43" s="4" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>G5</t>
         </is>
       </c>
       <c r="B43" s="4" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>G</t>
         </is>
       </c>
       <c r="C43" s="5" t="inlineStr">
         <is>
-          <t>第7期の保険料基準額は6,077円である</t>
-        </is>
-      </c>
-      <c r="D43" s="11" t="inlineStr">
-        <is>
-          <t>E3</t>
+          <t>交付金の成果指標の統計的な安定性</t>
+        </is>
+      </c>
+      <c r="D43" s="15" t="inlineStr">
+        <is>
+          <t>E5</t>
         </is>
       </c>
       <c r="E43" s="5" t="inlineStr">
         <is>
-          <t>断定</t>
+          <t>記述せず</t>
         </is>
       </c>
       <c r="F43" s="5" t="inlineStr">
         <is>
-          <t>見える化C1（介護保険事業計画報告値・令和8年7月30日受領）により平成30年度〜令和2年度の第1号保険料月額として確認</t>
+          <t>―</t>
         </is>
       </c>
       <c r="G43" s="5" t="inlineStr">
         <is>
-          <t>確定。内部整合による推定（剰余累計＋159円）が原典と一致した。不足資料No.10は解消</t>
+          <t>分子・分母の実数が未確認。「全国トップ級」等の表現を用いない（不足資料 No.5）</t>
         </is>
       </c>
     </row>
     <row r="44" ht="52" customHeight="1">
       <c r="A44" s="4" t="inlineStr">
         <is>
-          <t>H5</t>
+          <t>G6</t>
         </is>
       </c>
       <c r="B44" s="4" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>G</t>
         </is>
       </c>
       <c r="C44" s="5" t="inlineStr">
         <is>
-          <t>第9期の国標準13段階の乗率は0.455・0.685・0.690…2.40である</t>
-        </is>
-      </c>
-      <c r="D44" s="11" t="inlineStr">
-        <is>
-          <t>E3</t>
+          <t>第9期の19施策のうち13施策は計画記載上の評価可能性が低い</t>
+        </is>
+      </c>
+      <c r="D44" s="9" t="inlineStr">
+        <is>
+          <t>E2</t>
         </is>
       </c>
       <c r="E44" s="5" t="inlineStr">
@@ -2761,19 +2761,19 @@
       </c>
       <c r="F44" s="5" t="inlineStr">
         <is>
-          <t>介護保険法施行令の内容として、複数の自治体公表資料により確認</t>
+          <t>第9期計画 第5章の記載を確認</t>
         </is>
       </c>
       <c r="G44" s="5" t="inlineStr">
         <is>
-          <t>施行令の条文を直接確認していない。第10期の標準は政令改正により定まる（不足資料 No.11）</t>
+          <t>計画の記載の判定であり、施策の良否ではないことを明記済み</t>
         </is>
       </c>
     </row>
     <row r="45" ht="52" customHeight="1">
       <c r="A45" s="4" t="inlineStr">
         <is>
-          <t>H6</t>
+          <t>H1</t>
         </is>
       </c>
       <c r="B45" s="4" t="inlineStr">
@@ -2783,7 +2783,7 @@
       </c>
       <c r="C45" s="5" t="inlineStr">
         <is>
-          <t>低所得者軽減は他の被保険者の負担増になっていない</t>
+          <t>第9期の補正後被保険者数26,871人・算定上の基準額6,428円を再現できる</t>
         </is>
       </c>
       <c r="D45" s="9" t="inlineStr">
@@ -2793,12 +2793,12 @@
       </c>
       <c r="E45" s="5" t="inlineStr">
         <is>
-          <t>断定（試算）</t>
+          <t>断定</t>
         </is>
       </c>
       <c r="F45" s="5" t="inlineStr">
         <is>
-          <t>段階別の寄与分解（低所得層▲259.5人分に対し中高所得層＋476.3人分）</t>
+          <t>段階別被保険者数×公費軽減前の乗率の合計が公表値と完全一致</t>
         </is>
       </c>
       <c r="G45" s="5" t="inlineStr">
@@ -2810,54 +2810,54 @@
     <row r="46" ht="52" customHeight="1">
       <c r="A46" s="4" t="inlineStr">
         <is>
-          <t>C6</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="B46" s="4" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>H</t>
         </is>
       </c>
       <c r="C46" s="5" t="inlineStr">
         <is>
-          <t>上川管内21保険者のなかでは、当広域連合の給付月額指数1.08は8〜10位（比布町・剣淵町と同値）であり管内中位値1.05に近い</t>
-        </is>
-      </c>
-      <c r="D46" s="11" t="inlineStr">
-        <is>
-          <t>E3</t>
+          <t>16段階の設定により保険料基準額は国標準13段階の場合より月52円低い</t>
+        </is>
+      </c>
+      <c r="D46" s="9" t="inlineStr">
+        <is>
+          <t>E2</t>
         </is>
       </c>
       <c r="E46" s="5" t="inlineStr">
         <is>
-          <t>断定</t>
+          <t>断定（試算）</t>
         </is>
       </c>
       <c r="F46" s="5" t="inlineStr">
         <is>
-          <t>見える化D49（令和5年）。管内平均1.000、最大1.23（愛別町）、最小0.73（音威子府村）</t>
+          <t>本表の試算（乗率のみを置換）</t>
         </is>
       </c>
       <c r="G46" s="5" t="inlineStr">
         <is>
-          <t>「全国を上回る」ことと「管内で高い」ことは別である</t>
+          <t>段階の区分そのものも異なるため概算である旨を明記済み</t>
         </is>
       </c>
     </row>
     <row r="47" ht="52" customHeight="1">
       <c r="A47" s="4" t="inlineStr">
         <is>
-          <t>C7</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="B47" s="4" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>H</t>
         </is>
       </c>
       <c r="C47" s="5" t="inlineStr">
         <is>
-          <t>地域差指数の受給率×受給者単価は給付月額指数に一致しない</t>
+          <t>第9期は2年で約42百万円の剰余が生じている</t>
         </is>
       </c>
       <c r="D47" s="9" t="inlineStr">
@@ -2867,39 +2867,39 @@
       </c>
       <c r="E47" s="5" t="inlineStr">
         <is>
-          <t>断定</t>
+          <t>断定（概算と明記）</t>
         </is>
       </c>
       <c r="F47" s="5" t="inlineStr">
         <is>
-          <t>上川管内21保険者中16保険者で0.03を超えてずれる。全保険者で正の方向に偏る（平均＋0.063、大雪＋0.065）</t>
+          <t>見える化C1により令和6年度＋337円・令和7年度＋48円（累計385円／月）を確認。被保険者数約9,190人により金額換算</t>
         </is>
       </c>
       <c r="G47" s="5" t="inlineStr">
         <is>
-          <t>ずれが生じる理由（性・年齢調整の適用範囲、指数化の基準）は未確認（不足資料No.16）</t>
+          <t>月額の差は原典で確定した。金額換算は被保険者数の前提を含む。基金への積立実績との一致は未確認（不足資料 No.9）。令和6・7年度は年度途中までの集計である</t>
         </is>
       </c>
     </row>
     <row r="48" ht="52" customHeight="1">
       <c r="A48" s="4" t="inlineStr">
         <is>
-          <t>C8</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="B48" s="4" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>H</t>
         </is>
       </c>
       <c r="C48" s="5" t="inlineStr">
         <is>
-          <t>給付水準の高さは平成21年度から続く構造であり、17年間の伸びは管内で小さい方に属する</t>
-        </is>
-      </c>
-      <c r="D48" s="9" t="inlineStr">
-        <is>
-          <t>E2</t>
+          <t>第7期の保険料基準額は6,077円である</t>
+        </is>
+      </c>
+      <c r="D48" s="11" t="inlineStr">
+        <is>
+          <t>E3</t>
         </is>
       </c>
       <c r="E48" s="5" t="inlineStr">
@@ -2909,29 +2909,29 @@
       </c>
       <c r="F48" s="5" t="inlineStr">
         <is>
-          <t>見える化C1。平成21年度の給付月額21,490円は管内1位、令和7年度26,885円は12位。伸び率＋25.1％は管内16位（管内平均＋46.4％）</t>
+          <t>見える化C1（介護保険事業計画報告値・令和8年7月30日受領）により平成30年度〜令和2年度の第1号保険料月額として確認</t>
         </is>
       </c>
       <c r="G48" s="5" t="inlineStr">
         <is>
-          <t>令和6・7年度は年度途中までの集計である</t>
+          <t>確定。内部整合による推定（剰余累計＋159円）が原典と一致した。不足資料No.10は解消</t>
         </is>
       </c>
     </row>
     <row r="49" ht="52" customHeight="1">
       <c r="A49" s="4" t="inlineStr">
         <is>
-          <t>C9</t>
+          <t>H5</t>
         </is>
       </c>
       <c r="B49" s="4" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>H</t>
         </is>
       </c>
       <c r="C49" s="5" t="inlineStr">
         <is>
-          <t>令和7年度の必要保険料月額は6,352円で基準額6,400円との差は48円である</t>
+          <t>第9期の国標準13段階の乗率は0.455・0.685・0.690…2.40である</t>
         </is>
       </c>
       <c r="D49" s="11" t="inlineStr">
@@ -2946,29 +2946,29 @@
       </c>
       <c r="F49" s="5" t="inlineStr">
         <is>
-          <t>見える化C1。令和6年度の337円から縮小</t>
+          <t>介護保険法施行令の内容として、複数の自治体公表資料により確認</t>
         </is>
       </c>
       <c r="G49" s="5" t="inlineStr">
         <is>
-          <t>年度途中までの集計であり確定値により再計算する</t>
+          <t>施行令の条文を直接確認していない。第10期の標準は政令改正により定まる（不足資料 No.11）</t>
         </is>
       </c>
     </row>
     <row r="50" ht="52" customHeight="1">
       <c r="A50" s="4" t="inlineStr">
         <is>
-          <t>D6</t>
+          <t>H6</t>
         </is>
       </c>
       <c r="B50" s="4" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>H</t>
         </is>
       </c>
       <c r="C50" s="5" t="inlineStr">
         <is>
-          <t>3町の6区分平均の自給率は美瑛77.5％・東川67.1％・東神楽63.2％である</t>
+          <t>低所得者軽減は他の被保険者の負担増になっていない</t>
         </is>
       </c>
       <c r="D50" s="9" t="inlineStr">
@@ -2978,39 +2978,39 @@
       </c>
       <c r="E50" s="5" t="inlineStr">
         <is>
-          <t>断定</t>
+          <t>断定（試算）</t>
         </is>
       </c>
       <c r="F50" s="5" t="inlineStr">
         <is>
-          <t>見える化δ（令和7年9月）から算定</t>
+          <t>段階別の寄与分解（低所得層▲259.5人分に対し中高所得層＋476.3人分）</t>
         </is>
       </c>
       <c r="G50" s="5" t="inlineStr">
         <is>
-          <t>算定できる区分の単純平均である。給付額による加重平均には町別のサービス区分別給付費を要する（不足資料No.17）</t>
+          <t>―</t>
         </is>
       </c>
     </row>
     <row r="51" ht="52" customHeight="1">
       <c r="A51" s="4" t="inlineStr">
         <is>
-          <t>D7</t>
+          <t>C6</t>
         </is>
       </c>
       <c r="B51" s="4" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C51" s="5" t="inlineStr">
         <is>
-          <t>自給率と給付月額指数の間に関係は確認できない</t>
-        </is>
-      </c>
-      <c r="D51" s="9" t="inlineStr">
-        <is>
-          <t>E2</t>
+          <t>上川管内21保険者のなかでは、当広域連合の給付月額指数1.08は8〜10位（比布町・剣淵町と同値）であり管内中位値1.05に近い</t>
+        </is>
+      </c>
+      <c r="D51" s="11" t="inlineStr">
+        <is>
+          <t>E3</t>
         </is>
       </c>
       <c r="E51" s="5" t="inlineStr">
@@ -3020,34 +3020,34 @@
       </c>
       <c r="F51" s="5" t="inlineStr">
         <is>
-          <t>単一市町村保険者のうち自給率0.0％の2村を除く15件でr＝0.07</t>
+          <t>見える化D49（令和5年）。管内平均1.000、最大1.23（愛別町）、最小0.73（音威子府村）</t>
         </is>
       </c>
       <c r="G51" s="5" t="inlineStr">
         <is>
-          <t>2村を含めるとr＝0.53となるため、除外の理由を必ず併記する</t>
+          <t>「全国を上回る」ことと「管内で高い」ことは別である</t>
         </is>
       </c>
     </row>
     <row r="52" ht="52" customHeight="1">
       <c r="A52" s="4" t="inlineStr">
         <is>
-          <t>H7</t>
+          <t>C7</t>
         </is>
       </c>
       <c r="B52" s="4" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C52" s="5" t="inlineStr">
         <is>
-          <t>保険料基準額の推移は第5期5,100円→第6期5,776円→第7期6,077円→第8期6,300円→第9期6,400円である</t>
-        </is>
-      </c>
-      <c r="D52" s="11" t="inlineStr">
-        <is>
-          <t>E3</t>
+          <t>地域差指数の受給率×受給者単価は給付月額指数に一致しない</t>
+        </is>
+      </c>
+      <c r="D52" s="9" t="inlineStr">
+        <is>
+          <t>E2</t>
         </is>
       </c>
       <c r="E52" s="5" t="inlineStr">
@@ -3057,29 +3057,29 @@
       </c>
       <c r="F52" s="5" t="inlineStr">
         <is>
-          <t>見える化C1（介護保険事業計画報告値）</t>
+          <t>上川管内21保険者中16保険者で0.03を超えてずれる。全保険者で正の方向に偏る（平均＋0.063、大雪＋0.065）</t>
         </is>
       </c>
       <c r="G52" s="5" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>ずれが生じる理由（性・年齢調整の適用範囲、指数化の基準）は未確認（不足資料No.16）</t>
         </is>
       </c>
     </row>
     <row r="53" ht="52" customHeight="1">
       <c r="A53" s="4" t="inlineStr">
         <is>
-          <t>H8</t>
+          <t>C8</t>
         </is>
       </c>
       <c r="B53" s="4" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C53" s="5" t="inlineStr">
         <is>
-          <t>第9期において保険料が必要額を上回っている保険者は上川管内21のうち6にとどまる</t>
+          <t>給付水準の高さは平成21年度から続く構造であり、17年間の伸びは管内で小さい方に属する</t>
         </is>
       </c>
       <c r="D53" s="9" t="inlineStr">
@@ -3094,7 +3094,7 @@
       </c>
       <c r="F53" s="5" t="inlineStr">
         <is>
-          <t>見える化C1から算定。管内平均は▲400円で当広域連合の＋385円は逆方向</t>
+          <t>見える化C1。平成21年度の給付月額21,490円は管内1位、令和7年度26,885円は12位。伸び率＋25.1％は管内16位（管内平均＋46.4％）</t>
         </is>
       </c>
       <c r="G53" s="5" t="inlineStr">
@@ -3106,22 +3106,22 @@
     <row r="54" ht="52" customHeight="1">
       <c r="A54" s="4" t="inlineStr">
         <is>
-          <t>I1</t>
+          <t>C9</t>
         </is>
       </c>
       <c r="B54" s="4" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C54" s="5" t="inlineStr">
         <is>
-          <t>特定地域の指定基準は3段階の構造である</t>
-        </is>
-      </c>
-      <c r="D54" s="9" t="inlineStr">
-        <is>
-          <t>E1</t>
+          <t>令和7年度の必要保険料月額は6,352円で基準額6,400円との差は48円である</t>
+        </is>
+      </c>
+      <c r="D54" s="11" t="inlineStr">
+        <is>
+          <t>E3</t>
         </is>
       </c>
       <c r="E54" s="5" t="inlineStr">
@@ -3131,34 +3131,34 @@
       </c>
       <c r="F54" s="5" t="inlineStr">
         <is>
-          <t>第135回社会保障審議会介護保険部会 資料3の直接確認</t>
+          <t>見える化C1。令和6年度の337円から縮小</t>
         </is>
       </c>
       <c r="G54" s="5" t="inlineStr">
         <is>
-          <t>告示前の素案である旨を明記済み</t>
+          <t>年度途中までの集計であり確定値により再計算する</t>
         </is>
       </c>
     </row>
     <row r="55" ht="52" customHeight="1">
       <c r="A55" s="4" t="inlineStr">
         <is>
-          <t>I2</t>
+          <t>D6</t>
         </is>
       </c>
       <c r="B55" s="4" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>D</t>
         </is>
       </c>
       <c r="C55" s="5" t="inlineStr">
         <is>
-          <t>3町の地域指定は東川＝辺地・特豪、美瑛＝過疎・辺地・特豪、東神楽＝辺地</t>
+          <t>3町の6区分平均の自給率は美瑛77.5％・東川67.1％・東神楽63.2％である</t>
         </is>
       </c>
       <c r="D55" s="9" t="inlineStr">
         <is>
-          <t>E1</t>
+          <t>E2</t>
         </is>
       </c>
       <c r="E55" s="5" t="inlineStr">
@@ -3168,34 +3168,34 @@
       </c>
       <c r="F55" s="5" t="inlineStr">
         <is>
-          <t>地域指定一覧（令和8年4月1日現在）の直接確認</t>
+          <t>見える化δ（令和7年9月）から算定</t>
         </is>
       </c>
       <c r="G55" s="5" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>算定できる区分の単純平均である。給付額による加重平均には町別のサービス区分別給付費を要する（不足資料No.17）</t>
         </is>
       </c>
     </row>
     <row r="56" ht="52" customHeight="1">
       <c r="A56" s="4" t="inlineStr">
         <is>
-          <t>I3</t>
+          <t>D7</t>
         </is>
       </c>
       <c r="B56" s="4" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>D</t>
         </is>
       </c>
       <c r="C56" s="5" t="inlineStr">
         <is>
-          <t>美瑛町の町道除雪率は52.9％、スクールバスは10路線である</t>
+          <t>自給率と給付月額指数の間に関係は確認できない</t>
         </is>
       </c>
       <c r="D56" s="9" t="inlineStr">
         <is>
-          <t>E1</t>
+          <t>E2</t>
         </is>
       </c>
       <c r="E56" s="5" t="inlineStr">
@@ -3205,101 +3205,286 @@
       </c>
       <c r="F56" s="5" t="inlineStr">
         <is>
-          <t>美瑛町過疎地域持続的発展市町村計画の直接確認</t>
+          <t>単一市町村保険者のうち自給率0.0％の2村を除く15件でr＝0.07</t>
         </is>
       </c>
       <c r="G56" s="5" t="inlineStr">
         <is>
-          <t>令和3〜7年度計画の値であり、最新の実績ではない</t>
+          <t>2村を含めるとr＝0.53となるため、除外の理由を必ず併記する</t>
         </is>
       </c>
     </row>
     <row r="57" ht="52" customHeight="1">
       <c r="A57" s="4" t="inlineStr">
         <is>
-          <t>I4</t>
+          <t>H7</t>
         </is>
       </c>
       <c r="B57" s="4" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>H</t>
         </is>
       </c>
       <c r="C57" s="5" t="inlineStr">
         <is>
-          <t>朗根内地区は訪問・通所困難地域に該当する可能性が最も高い</t>
-        </is>
-      </c>
-      <c r="D57" s="13" t="inlineStr">
-        <is>
-          <t>E4</t>
+          <t>保険料基準額の推移は第5期5,100円→第6期5,776円→第7期6,077円→第8期6,300円→第9期6,400円である</t>
+        </is>
+      </c>
+      <c r="D57" s="11" t="inlineStr">
+        <is>
+          <t>E3</t>
         </is>
       </c>
       <c r="E57" s="5" t="inlineStr">
         <is>
-          <t>推量で記述</t>
+          <t>断定</t>
         </is>
       </c>
       <c r="F57" s="5" t="inlineStr">
         <is>
-          <t>人口233人、スクールバス依存、除雪率52.9％の組合せ</t>
+          <t>見える化C1（介護保険事業計画報告値）</t>
         </is>
       </c>
       <c r="G57" s="5" t="inlineStr">
         <is>
-          <t>事業所の通常の事業の実施地域を確認していないため、判定の根拠そのものが未取得（不足資料 No.2）</t>
+          <t>―</t>
         </is>
       </c>
     </row>
     <row r="58" ht="52" customHeight="1">
       <c r="A58" s="4" t="inlineStr">
         <is>
+          <t>H8</t>
+        </is>
+      </c>
+      <c r="B58" s="4" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="C58" s="5" t="inlineStr">
+        <is>
+          <t>第9期において保険料が必要額を上回っている保険者は上川管内21のうち6にとどまる</t>
+        </is>
+      </c>
+      <c r="D58" s="9" t="inlineStr">
+        <is>
+          <t>E2</t>
+        </is>
+      </c>
+      <c r="E58" s="5" t="inlineStr">
+        <is>
+          <t>断定</t>
+        </is>
+      </c>
+      <c r="F58" s="5" t="inlineStr">
+        <is>
+          <t>見える化C1から算定。管内平均は▲400円で当広域連合の＋385円は逆方向</t>
+        </is>
+      </c>
+      <c r="G58" s="5" t="inlineStr">
+        <is>
+          <t>令和6・7年度は年度途中までの集計である</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="52" customHeight="1">
+      <c r="A59" s="4" t="inlineStr">
+        <is>
+          <t>I1</t>
+        </is>
+      </c>
+      <c r="B59" s="4" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="C59" s="5" t="inlineStr">
+        <is>
+          <t>特定地域の指定基準は3段階の構造である</t>
+        </is>
+      </c>
+      <c r="D59" s="9" t="inlineStr">
+        <is>
+          <t>E1</t>
+        </is>
+      </c>
+      <c r="E59" s="5" t="inlineStr">
+        <is>
+          <t>断定</t>
+        </is>
+      </c>
+      <c r="F59" s="5" t="inlineStr">
+        <is>
+          <t>第135回社会保障審議会介護保険部会 資料3の直接確認</t>
+        </is>
+      </c>
+      <c r="G59" s="5" t="inlineStr">
+        <is>
+          <t>告示前の素案である旨を明記済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="52" customHeight="1">
+      <c r="A60" s="4" t="inlineStr">
+        <is>
+          <t>I2</t>
+        </is>
+      </c>
+      <c r="B60" s="4" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="C60" s="5" t="inlineStr">
+        <is>
+          <t>3町の地域指定は東川＝辺地・特豪、美瑛＝過疎・辺地・特豪、東神楽＝辺地</t>
+        </is>
+      </c>
+      <c r="D60" s="9" t="inlineStr">
+        <is>
+          <t>E1</t>
+        </is>
+      </c>
+      <c r="E60" s="5" t="inlineStr">
+        <is>
+          <t>断定</t>
+        </is>
+      </c>
+      <c r="F60" s="5" t="inlineStr">
+        <is>
+          <t>地域指定一覧（令和8年4月1日現在）の直接確認</t>
+        </is>
+      </c>
+      <c r="G60" s="5" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="52" customHeight="1">
+      <c r="A61" s="4" t="inlineStr">
+        <is>
+          <t>I3</t>
+        </is>
+      </c>
+      <c r="B61" s="4" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="C61" s="5" t="inlineStr">
+        <is>
+          <t>美瑛町の町道除雪率は52.9％、スクールバスは10路線である</t>
+        </is>
+      </c>
+      <c r="D61" s="9" t="inlineStr">
+        <is>
+          <t>E1</t>
+        </is>
+      </c>
+      <c r="E61" s="5" t="inlineStr">
+        <is>
+          <t>断定</t>
+        </is>
+      </c>
+      <c r="F61" s="5" t="inlineStr">
+        <is>
+          <t>美瑛町過疎地域持続的発展市町村計画の直接確認</t>
+        </is>
+      </c>
+      <c r="G61" s="5" t="inlineStr">
+        <is>
+          <t>令和3〜7年度計画の値であり、最新の実績ではない</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="52" customHeight="1">
+      <c r="A62" s="4" t="inlineStr">
+        <is>
+          <t>I4</t>
+        </is>
+      </c>
+      <c r="B62" s="4" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="C62" s="5" t="inlineStr">
+        <is>
+          <t>朗根内地区は訪問・通所困難地域に該当する可能性が最も高い</t>
+        </is>
+      </c>
+      <c r="D62" s="13" t="inlineStr">
+        <is>
+          <t>E4</t>
+        </is>
+      </c>
+      <c r="E62" s="5" t="inlineStr">
+        <is>
+          <t>推量で記述</t>
+        </is>
+      </c>
+      <c r="F62" s="5" t="inlineStr">
+        <is>
+          <t>人口233人、スクールバス依存、除雪率52.9％の組合せ</t>
+        </is>
+      </c>
+      <c r="G62" s="5" t="inlineStr">
+        <is>
+          <t>事業所の通常の事業の実施地域を確認していないため、判定の根拠そのものが未取得（不足資料 No.2）</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="52" customHeight="1">
+      <c r="A63" s="4" t="inlineStr">
+        <is>
           <t>I5</t>
         </is>
       </c>
-      <c r="B58" s="4" t="inlineStr">
+      <c r="B63" s="4" t="inlineStr">
         <is>
           <t>I</t>
         </is>
       </c>
-      <c r="C58" s="5" t="inlineStr">
+      <c r="C63" s="5" t="inlineStr">
         <is>
           <t>小学校区と第9期の6圏域の対応関係</t>
         </is>
       </c>
-      <c r="D58" s="15" t="inlineStr">
+      <c r="D63" s="15" t="inlineStr">
         <is>
           <t>E5</t>
         </is>
       </c>
-      <c r="E58" s="5" t="inlineStr">
+      <c r="E63" s="5" t="inlineStr">
         <is>
           <t>記述せず</t>
         </is>
       </c>
-      <c r="F58" s="5" t="inlineStr">
+      <c r="F63" s="5" t="inlineStr">
         <is>
           <t>―</t>
         </is>
       </c>
-      <c r="G58" s="5" t="inlineStr">
+      <c r="G63" s="5" t="inlineStr">
         <is>
           <t>美馬牛小学校区以外は対応が不明。美瑛町への確認を要する（不足資料 No.12）</t>
         </is>
       </c>
     </row>
-    <row r="60" ht="48" customHeight="1">
-      <c r="A60" s="17" t="inlineStr">
-        <is>
-          <t>注1）No.の網掛けは、E4・E5でありながら断定形で記述しているもの（8件）である。03シートで対応を示す。注2）「記述の形」の区分は次のとおり。断定＝「〜である」「〜します」等の断定形。断定（留保付き）＝断定形だが留保を併記している。推量で記述＝「〜の可能性がある」「〜と考えられる」等。記述せず＝主張として書いていない。前提の選択として明示＝推計の前提であり事実の主張ではないことを明示。注3）本表の54件は、成果物に含まれる主要な主張を網羅する意図で領域ごとに抽出したものである。数値の引用や図表の説明など、事実の記述にとどまるものは含めていない。</t>
+    <row r="65" ht="48" customHeight="1">
+      <c r="A65" s="17" t="inlineStr">
+        <is>
+          <t>注1）No.の網掛けは、E4・E5でありながら断定形で記述しているもの（8件）である。03シートで対応を示す。注2）「記述の形」の区分は次のとおり。断定＝「〜である」「〜します」等の断定形。断定（留保付き）＝断定形だが留保を併記している。推量で記述＝「〜の可能性がある」「〜と考えられる」等。記述せず＝主張として書いていない。前提の選択として明示＝推計の前提であり事実の主張ではないことを明示。注3）本表の59件は、成果物に含まれる主要な主張を網羅する意図で領域ごとに抽出したものである。数値の引用や図表の説明など、事実の記述にとどまるものは含めていない。</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="A60:G60"/>
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A65:G65"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3407,23 +3592,23 @@
         <v>0</v>
       </c>
       <c r="D5" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E5" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="F5" s="8" t="n">
         <v>2</v>
-      </c>
-      <c r="F5" s="8" t="n">
-        <v>1</v>
       </c>
       <c r="G5" s="8" t="n">
         <v>0</v>
       </c>
       <c r="H5" s="8" t="n">
-        <v>4</v>
-      </c>
-      <c r="I5" s="13" t="inlineStr">
-        <is>
-          <t>25％</t>
+        <v>9</v>
+      </c>
+      <c r="I5" s="15" t="inlineStr">
+        <is>
+          <t>22％</t>
         </is>
       </c>
       <c r="J5" s="5" t="inlineStr"/>
@@ -3751,19 +3936,19 @@
         <v>4</v>
       </c>
       <c r="D14" s="20" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E14" s="20" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="F14" s="20" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G14" s="20" t="n">
         <v>7</v>
       </c>
       <c r="H14" s="20" t="n">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="I14" s="19" t="inlineStr">
         <is>
@@ -3862,7 +4047,7 @@
         </is>
       </c>
       <c r="B19" s="8" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C19" s="8" t="n">
         <v>1</v>
@@ -3877,7 +4062,7 @@
         <v>0</v>
       </c>
       <c r="G19" s="8" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="H19" s="5" t="inlineStr"/>
       <c r="I19" s="5" t="inlineStr"/>
@@ -3894,7 +4079,7 @@
         </is>
       </c>
       <c r="B20" s="8" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C20" s="8" t="n">
         <v>0</v>
@@ -3909,7 +4094,7 @@
         <v>0</v>
       </c>
       <c r="G20" s="8" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="H20" s="5" t="inlineStr"/>
       <c r="I20" s="5" t="inlineStr"/>
@@ -3937,7 +4122,7 @@
         <v>0</v>
       </c>
       <c r="G21" s="8" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H21" s="5" t="inlineStr"/>
       <c r="I21" s="5" t="inlineStr"/>
@@ -3982,7 +4167,7 @@
     <row r="24" ht="28" customHeight="1">
       <c r="A24" s="17" t="inlineStr">
         <is>
-          <t>注1）E4・E5は合わせて13件で全体の24％を占める。このうち断定形で記述しているのは6件であり、03シートで対応する。注2）領域別では、C（給付費・受給率・単価）とD（供給基盤）でE4・E5の割合が高い。いずれも保険者・3町が保有する台帳・実績データを要するものであり、資料の受領により水準を引き上げられる。注3）F（住民の状態・行動）は個票データを受領しているためE2が多い。調査に基づく主張は根拠の水準が高い。</t>
+          <t>注1）E4・E5は合わせて14件で全体の24％を占める。このうち断定形で記述しているのは6件であり、03シートで対応する。注2）領域別では、C（給付費・受給率・単価）とD（供給基盤）でE4・E5の割合が高い。いずれも保険者・3町が保有する台帳・実績データを要するものであり、資料の受領により水準を引き上げられる。注3）F（住民の状態・行動）は個票データを受領しているためE2が多い。調査に基づく主張は根拠の水準が高い。</t>
         </is>
       </c>
     </row>

--- a/output/第10期計画_主張の根拠水準の棚卸しと再レビュー.xlsx
+++ b/output/第10期計画_主張の根拠水準の棚卸しと再レビュー.xlsx
@@ -12,7 +12,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02_根拠水準別の集計" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03_断定している仮説の特定" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04_逆転が起きた2件の共通原因" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05_レッドチーム再レビュー" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05_追加自己点検" sheetId="6" state="visible" r:id="rId6"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06_不足資料一覧" sheetId="7" state="visible" r:id="rId7"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07_記述ルール" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
@@ -628,7 +628,7 @@
     <row r="2" ht="56" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>レッドチームレビューの指摘のうち2件（No.5 3町の数値目標、No.1 認定率の年齢調整）で検証結果が当初の説明と逆転したことを受け、全成果物の主張を棚卸しし、根拠の水準を分類したうえで、仮説を断定形で記述している箇所を特定する。分類の枠組みは、領域（9区分）と根拠水準（5階層）の2軸とし、いずれも重複なく全体を覆う。作成日：令和8年7月29日。</t>
+          <t>自己点検記録の指摘のうち2件（No.5 3町の数値目標、No.1 認定率の年齢調整）で検証結果が当初の説明と逆転したことを受け、全成果物の主張を棚卸しし、根拠の水準を分類したうえで、仮説を断定形で記述している箇所を特定する。分類の枠組みは、領域（9区分）と根拠水準（5階層）の2軸とし、いずれも重複なく全体を覆う。作成日：令和8年7月29日。</t>
         </is>
       </c>
     </row>
@@ -765,7 +765,7 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>05_レッドチーム再レビュー</t>
+          <t>05_追加自己点検</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="G13" s="5" t="inlineStr">
         <is>
-          <t>撤回した。令和5年の差1.10ポイントのうち分子（高齢者数）の寄与＋0.64ポイントが分母（総人口）の寄与＋0.46ポイントを上回る。レッドチームレビューNo.23の指摘が的中した（人口推計の基礎の検証04シート）</t>
+          <t>撤回した。令和5年の差1.10ポイントのうち分子（高齢者数）の寄与＋0.64ポイントが分母（総人口）の寄与＋0.46ポイントを上回る。自己点検記録No.23の指摘のとおりであることが確認された（人口推計の基礎の検証04シート）</t>
         </is>
       </c>
     </row>
@@ -4210,7 +4210,7 @@
     <row r="2" ht="56" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>E4・E5でありながら断定形で記述している箇所を特定し、改める記述と、確定に必要な資料を示す。これらは、レッドチームレビューで逆転した2件と同じ構造を持つ。</t>
+          <t>E4・E5でありながら断定形で記述している箇所を特定し、改める記述と、確定に必要な資料を示す。これらは、自己点検記録で逆転した2件と同じ構造を持つ。</t>
         </is>
       </c>
     </row>
@@ -4476,7 +4476,7 @@
     <row r="12" ht="36" customHeight="1">
       <c r="A12" s="17" t="inlineStr">
         <is>
-          <t>注1）8件のうち6件（A1・C1・C2・C3・D3・D4・F4・G3のうちF4を除く7件から資料不要のものを除く）は、資料の受領により水準を引き上げられる。F4は記述の限定のみで対応できる。注2）これらは、レッドチームレビューで逆転した2件と同じ構造を持つ。①部分的な観測から全体を述べている（A1・C2・C3）、②観測を説明する仮説を検証せずに事実として記述している（C1・D3・F4・G3）。注3）改める記述は、事実として確認できる部分と、推論にとどまる部分を分けて書いたものである。計画本文でも同じ方針で記述する。</t>
+          <t>注1）8件のうち6件（A1・C1・C2・C3・D3・D4・F4・G3のうちF4を除く7件から資料不要のものを除く）は、資料の受領により水準を引き上げられる。F4は記述の限定のみで対応できる。注2）これらは、自己点検記録で逆転した2件と同じ構造を持つ。①部分的な観測から全体を述べている（A1・C2・C3）、②観測を説明する仮説を検証せずに事実として記述している（C1・D3・F4・G3）。注3）改める記述は、事実として確認できる部分と、推論にとどまる部分を分けて書いたものである。計画本文でも同じ方針で記述する。</t>
         </is>
       </c>
     </row>
@@ -4516,7 +4516,7 @@
     <row r="2" ht="56" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>レッドチームレビューのNo.5（3町の数値目標）とNo.1（認定率の年齢調整）で、検証結果が当初の説明と逆転した。原因を分析し、同じ失敗が他の主張にも起きていないかを点検する。</t>
+          <t>自己点検記録のNo.5（3町の数値目標）とNo.1（認定率の年齢調整）で、検証結果が当初の説明と逆転した。原因を分析し、同じ失敗が他の主張にも起きていないかを点検する。</t>
         </is>
       </c>
     </row>
@@ -4745,7 +4745,7 @@
       <c r="D16" s="7" t="n"/>
       <c r="E16" s="5" t="inlineStr">
         <is>
-          <t>主張ごとに反証条件を明示する。レッドチームレビュー06シートで実施済み。今後は主張と同時に作成する</t>
+          <t>主張ごとに反証条件を明示する。自己点検記録06シートで実施済み。今後は主張と同時に作成する</t>
         </is>
       </c>
     </row>
@@ -4815,7 +4815,7 @@
     <row r="21" ht="36" customHeight="1">
       <c r="A21" s="17" t="inlineStr">
         <is>
-          <t>注1）2件の逆転は、いずれも受託者の自己点検（レッドチームレビュー）により指摘され、資料の受領により検証されたものである。委員会や北海道からの指摘を受けて発覚したものではない。注2）ただし、自己点検で気づけたのは「指摘した箇所」だけである。本表03シートの8件は同じ構造を持つ主張であり、資料が得られれば逆転する可能性がある。</t>
+          <t>注1）2件の逆転は、いずれも受託者の自己点検（自己点検記録）により指摘され、資料の受領により検証されたものである。委員会や北海道からの指摘を受けて発覚したものではない。注2）ただし、自己点検で気づけたのは「指摘した箇所」だけである。本表03シートの8件は同じ構造を持つ主張であり、資料が得られれば逆転する可能性がある。</t>
         </is>
       </c>
     </row>
@@ -4863,7 +4863,7 @@
     <row r="2" ht="56" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>04シートで特定した2つの共通原因に照らして、既存のレッドチームレビュー18件では指摘していなかった箇所を再点検する。重大度の定義は既存のレビューと同じ。</t>
+          <t>04シートで特定した2つの共通原因に照らして、既存の自己点検記録18件では指摘していなかった箇所を再点検する。重大度の定義は既存のレビューと同じ。</t>
         </is>
       </c>
     </row>
@@ -5142,7 +5142,7 @@
     <row r="14" ht="36" customHeight="1">
       <c r="A14" s="17" t="inlineStr">
         <is>
-          <t>注1）本シートの8件は、既存のレッドチームレビュー18件に追加するものである。追加後の総数は26件（重大9・中13・軽微4）となる。注2）新規8件のうち、資料の受領を要するのは4件（No.19・20・22・24）である。他の4件は記述の限定により対応できる。注3）No.19・No.20を重大としたのは、指摘が正しければ所見の結論が変わるためである。No.19は第6章の整備方針の根拠に、No.20は第9期の評価の対象期間そのものに関わる。</t>
+          <t>注1）本シートの8件は、既存の自己点検記録18件に追加するものである。追加後の総数は26件（重大9・中13・軽微4）となる。注2）新規8件のうち、資料の受領を要するのは4件（No.19・20・22・24）である。他の4件は記述の限定により対応できる。注3）No.19・No.20を重大としたのは、指摘が正しければ所見の結論が変わるためである。No.19は第6章の整備方針の根拠に、No.20は第9期の評価の対象期間そのものに関わる。</t>
         </is>
       </c>
     </row>
